--- a/eval/labeling_sheet.xlsx
+++ b/eval/labeling_sheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="작성법" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="라벨링" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="영상목록" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="진행현황" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성법" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="라벨링" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="영상목록" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="진행현황" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -86,7 +86,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -106,11 +106,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4E4"/>
       </patternFill>
     </fill>
   </fills>
@@ -140,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -192,9 +187,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -5729,7 +5721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5956,12 +5948,12 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>FUwnak8FyBI</t>
+          <t>uncSsiLbz1E</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>35,234개 레시피 중 1등한 라면</t>
+          <t>요리 레시피 쇼츠</t>
         </is>
       </c>
       <c r="D8" s="16" t="inlineStr">
@@ -5970,129 +5962,441 @@
         </is>
       </c>
       <c r="E8" s="15" t="n">
-        <v>37.9</v>
+        <v>29</v>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=FUwnak8FyBI</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="H8" s="15" t="inlineStr"/>
+          <t>https://www.youtube.com/watch?v=uncSsiLbz1E</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="n"/>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="15" t="n"/>
-      <c r="F9" s="16" t="n"/>
-      <c r="G9" s="15" t="n"/>
-      <c r="H9" s="15" t="n"/>
+      <c r="A9" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>z8QPN-ITUvI</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>도파민 터지는 참치비빔칼국수</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=z8QPN-ITUvI</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n"/>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="15" t="n"/>
-      <c r="F10" s="16" t="n"/>
-      <c r="G10" s="15" t="n"/>
-      <c r="H10" s="15" t="n"/>
+      <c r="A10" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>igP4-Rq5zgM</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>사리곰탕 파스타 #shorts #쇼츠 #사리곰탕면 #사리곰탕 #자취요리 #쉬운요리 #요리 #라면 #집밥요리 #간단한요리 #점심메뉴 #집밥 #사리곰탕파스타 #한국라면 #크림파스타</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=igP4-Rq5zgM</t>
+        </is>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="n"/>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="16" t="n"/>
-      <c r="D11" s="16" t="n"/>
-      <c r="E11" s="15" t="n"/>
-      <c r="F11" s="16" t="n"/>
-      <c r="G11" s="15" t="n"/>
-      <c r="H11" s="15" t="n"/>
+      <c r="A11" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Zlo2JQzihwc</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>성시경이 감탄한 1등 레시피 미친 조합! #성시경 #라면레시피 #쇼츠</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>119.1</v>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Zlo2JQzihwc</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n"/>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="15" t="n"/>
-      <c r="F12" s="16" t="n"/>
-      <c r="G12" s="15" t="n"/>
-      <c r="H12" s="15" t="n"/>
+      <c r="A12" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>5AP-rJGheKk</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>요리 레시피 쇼츠</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>후딱 레시피 Huttak</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5AP-rJGheKk</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="n"/>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="15" t="n"/>
-      <c r="F13" s="16" t="n"/>
-      <c r="G13" s="15" t="n"/>
-      <c r="H13" s="15" t="n"/>
+      <c r="A13" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>jPqpNbPT7yY</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>명절 전부치기 동태전 혼자서도 쉽게 쉽게 노릇하고 바삭하게 #집밥 #제철음식 #cooking #레시피 #반찬 #food #shourt #쇼츠</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>후딱 레시피 Huttak</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=jPqpNbPT7yY</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="n"/>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="16" t="n"/>
-      <c r="E14" s="15" t="n"/>
-      <c r="F14" s="16" t="n"/>
-      <c r="G14" s="15" t="n"/>
-      <c r="H14" s="15" t="n"/>
+      <c r="A14" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>282ScDPvm28</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>짜장! 재료도 간단! 만들기도 간단! #shorts</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>후딱 레시피 Huttak</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=282ScDPvm28</t>
+        </is>
+      </c>
+      <c r="G14" s="15" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+      <c r="H14" s="15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="n"/>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="16" t="n"/>
-      <c r="D15" s="16" t="n"/>
-      <c r="E15" s="15" t="n"/>
-      <c r="F15" s="16" t="n"/>
-      <c r="G15" s="15" t="n"/>
-      <c r="H15" s="15" t="n"/>
+      <c r="A15" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>sPeEcFdaD0M</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>너무 쉬워서 매일 먹는 두부 계란요리 Easy Tofu Egg Recipe</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>후딱 레시피 Huttak</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=sPeEcFdaD0M</t>
+        </is>
+      </c>
+      <c r="G15" s="15" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="n"/>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="16" t="n"/>
-      <c r="D16" s="16" t="n"/>
-      <c r="E16" s="15" t="n"/>
-      <c r="F16" s="16" t="n"/>
-      <c r="G16" s="15" t="n"/>
-      <c r="H16" s="15" t="n"/>
+      <c r="A16" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>rfkc9X4BItc</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>입맛 없을 때 무조건 해보세요! 오징어 초무침 황금 레시피 #간단요리 #반찬만들기 #오징어</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>후딱 레시피 Huttak</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=rfkc9X4BItc</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n"/>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="15" t="n"/>
-      <c r="F17" s="16" t="n"/>
-      <c r="G17" s="15" t="n"/>
-      <c r="H17" s="15" t="n"/>
+      <c r="A17" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>Hwzl8IA9NH0</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>말도 안 되는 맛</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>후딱 레시피 Huttak</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Hwzl8IA9NH0</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="n"/>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="15" t="n"/>
-      <c r="F18" s="16" t="n"/>
-      <c r="G18" s="15" t="n"/>
-      <c r="H18" s="15" t="n"/>
+      <c r="A18" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>11C8XqWobjQ</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>[⭐️490만⭐️] 초간단 4분 잔치국수 뚝딱! #shorts</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>후딱 레시피 Huttak</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=11C8XqWobjQ</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="n"/>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="16" t="n"/>
-      <c r="D19" s="16" t="n"/>
-      <c r="E19" s="15" t="n"/>
-      <c r="F19" s="16" t="n"/>
-      <c r="G19" s="15" t="n"/>
-      <c r="H19" s="15" t="n"/>
+      <c r="A19" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>iDMyw61V1XM</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>지코바는 사 먹지 마세요!</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>후딱 레시피 Huttak</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>55</v>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=iDMyw61V1XM</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="n"/>
@@ -6284,15 +6588,125 @@
       <c r="G38" s="15" t="n"/>
       <c r="H38" s="15" t="n"/>
     </row>
-    <row r="40" ht="26" customHeight="1">
-      <c r="A40" s="19" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="15" t="n"/>
+      <c r="B39" s="16" t="n"/>
+      <c r="C39" s="16" t="n"/>
+      <c r="D39" s="16" t="n"/>
+      <c r="E39" s="15" t="n"/>
+      <c r="F39" s="16" t="n"/>
+      <c r="G39" s="15" t="n"/>
+      <c r="H39" s="15" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="n"/>
+      <c r="B40" s="16" t="n"/>
+      <c r="C40" s="16" t="n"/>
+      <c r="D40" s="16" t="n"/>
+      <c r="E40" s="15" t="n"/>
+      <c r="F40" s="16" t="n"/>
+      <c r="G40" s="15" t="n"/>
+      <c r="H40" s="15" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="n"/>
+      <c r="B41" s="16" t="n"/>
+      <c r="C41" s="16" t="n"/>
+      <c r="D41" s="16" t="n"/>
+      <c r="E41" s="15" t="n"/>
+      <c r="F41" s="16" t="n"/>
+      <c r="G41" s="15" t="n"/>
+      <c r="H41" s="15" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="n"/>
+      <c r="B42" s="16" t="n"/>
+      <c r="C42" s="16" t="n"/>
+      <c r="D42" s="16" t="n"/>
+      <c r="E42" s="15" t="n"/>
+      <c r="F42" s="16" t="n"/>
+      <c r="G42" s="15" t="n"/>
+      <c r="H42" s="15" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="n"/>
+      <c r="B43" s="16" t="n"/>
+      <c r="C43" s="16" t="n"/>
+      <c r="D43" s="16" t="n"/>
+      <c r="E43" s="15" t="n"/>
+      <c r="F43" s="16" t="n"/>
+      <c r="G43" s="15" t="n"/>
+      <c r="H43" s="15" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="n"/>
+      <c r="B44" s="16" t="n"/>
+      <c r="C44" s="16" t="n"/>
+      <c r="D44" s="16" t="n"/>
+      <c r="E44" s="15" t="n"/>
+      <c r="F44" s="16" t="n"/>
+      <c r="G44" s="15" t="n"/>
+      <c r="H44" s="15" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="n"/>
+      <c r="B45" s="16" t="n"/>
+      <c r="C45" s="16" t="n"/>
+      <c r="D45" s="16" t="n"/>
+      <c r="E45" s="15" t="n"/>
+      <c r="F45" s="16" t="n"/>
+      <c r="G45" s="15" t="n"/>
+      <c r="H45" s="15" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="15" t="n"/>
+      <c r="B46" s="16" t="n"/>
+      <c r="C46" s="16" t="n"/>
+      <c r="D46" s="16" t="n"/>
+      <c r="E46" s="15" t="n"/>
+      <c r="F46" s="16" t="n"/>
+      <c r="G46" s="15" t="n"/>
+      <c r="H46" s="15" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="15" t="n"/>
+      <c r="B47" s="16" t="n"/>
+      <c r="C47" s="16" t="n"/>
+      <c r="D47" s="16" t="n"/>
+      <c r="E47" s="15" t="n"/>
+      <c r="F47" s="16" t="n"/>
+      <c r="G47" s="15" t="n"/>
+      <c r="H47" s="15" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="15" t="n"/>
+      <c r="B48" s="16" t="n"/>
+      <c r="C48" s="16" t="n"/>
+      <c r="D48" s="16" t="n"/>
+      <c r="E48" s="15" t="n"/>
+      <c r="F48" s="16" t="n"/>
+      <c r="G48" s="15" t="n"/>
+      <c r="H48" s="15" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="15" t="n"/>
+      <c r="B49" s="16" t="n"/>
+      <c r="C49" s="16" t="n"/>
+      <c r="D49" s="16" t="n"/>
+      <c r="E49" s="15" t="n"/>
+      <c r="F49" s="16" t="n"/>
+      <c r="G49" s="15" t="n"/>
+      <c r="H49" s="15" t="n"/>
+    </row>
+    <row r="51" ht="26" customHeight="1">
+      <c r="A51" s="18" t="inlineStr">
         <is>
           <t>· '질문 대상' 칸에 O 를 적은 영상에만 질문을 만듭니다. 저장 영상 25개 중 12~15개만 O 로 두고, 나머지는 검색 난이도를 유지하는 오답 후보로 남겨둡니다.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="26" customHeight="1">
-      <c r="A41" s="19" t="inlineStr">
+    <row r="52" ht="26" customHeight="1">
+      <c r="A52" s="18" t="inlineStr">
         <is>
           <t>· 상태가 ready 가 아닌 영상은 분석이 끝나지 않은 것입니다. 질문 대상에서 제외하세요.</t>
         </is>
@@ -6300,9 +6714,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A41:H41"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A52:H52"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -6311,6 +6725,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6377,7 +6802,7 @@
         <f>COUNTA(라벨링!$A$3:$A$2000)</f>
         <v/>
       </c>
-      <c r="C4" s="20" t="inlineStr"/>
+      <c r="C4" s="19" t="inlineStr"/>
       <c r="D4" s="15" t="inlineStr"/>
     </row>
     <row r="5">
@@ -6390,7 +6815,7 @@
         <f>IFERROR(SUMPRODUCT((라벨링!$A$3:$A$2000&lt;&gt;"")/COUNTIF(라벨링!$A$3:$A$2000,라벨링!$A$3:$A$2000&amp;"")),0)</f>
         <v/>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>45 ~ 55</t>
         </is>
@@ -6410,7 +6835,7 @@
         <f>IFERROR(SUMPRODUCT((라벨링!$H$3:$H$2000&lt;&gt;"")/COUNTIF(라벨링!$H$3:$H$2000,라벨링!$H$3:$H$2000&amp;"")),0)</f>
         <v/>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -6421,7 +6846,7 @@
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>유형별 2점(정확) 라벨 수 — 비슷하게 맞추세요</t>
         </is>
@@ -6437,7 +6862,7 @@
         <f>COUNTIFS(라벨링!$D$3:$D$2000,"재료분량",라벨링!$G$3:$G$2000,2)</f>
         <v/>
       </c>
-      <c r="C8" s="20" t="inlineStr"/>
+      <c r="C8" s="19" t="inlineStr"/>
       <c r="D8" s="15" t="inlineStr"/>
     </row>
     <row r="9">
@@ -6450,7 +6875,7 @@
         <f>COUNTIFS(라벨링!$D$3:$D$2000,"순서타이밍",라벨링!$G$3:$G$2000,2)</f>
         <v/>
       </c>
-      <c r="C9" s="20" t="inlineStr"/>
+      <c r="C9" s="19" t="inlineStr"/>
       <c r="D9" s="15" t="inlineStr"/>
     </row>
     <row r="10">
@@ -6463,7 +6888,7 @@
         <f>COUNTIFS(라벨링!$D$3:$D$2000,"시각적상태",라벨링!$G$3:$G$2000,2)</f>
         <v/>
       </c>
-      <c r="C10" s="20" t="inlineStr"/>
+      <c r="C10" s="19" t="inlineStr"/>
       <c r="D10" s="15" t="inlineStr"/>
     </row>
     <row r="11">
@@ -6476,7 +6901,7 @@
         <f>MAX(B8:B10)-MIN(B8:B10)</f>
         <v/>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>5 이하</t>
         </is>
@@ -6487,7 +6912,7 @@
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>검증 항목</t>
         </is>
@@ -6503,7 +6928,7 @@
         <f>COUNTIF(라벨링!$G$3:$G$2000,"없음")</f>
         <v/>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>5 ~ 8</t>
         </is>
@@ -6523,7 +6948,7 @@
         <f>COUNTIF(라벨링!$G$3:$G$2000,2)</f>
         <v/>
       </c>
-      <c r="C14" s="20" t="inlineStr"/>
+      <c r="C14" s="19" t="inlineStr"/>
       <c r="D14" s="15" t="inlineStr"/>
     </row>
     <row r="15">
@@ -6536,18 +6961,18 @@
         <f>COUNTIF(라벨링!$G$3:$G$2000,1)</f>
         <v/>
       </c>
-      <c r="C15" s="20" t="inlineStr"/>
+      <c r="C15" s="19" t="inlineStr"/>
       <c r="D15" s="15" t="inlineStr"/>
     </row>
     <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>※ '유형 간 최대 격차' 는 세 유형의 2점 라벨 수 중 최대-최소 차이입니다. 한 유형만 많으면 유형별 성능 비교가 흔들립니다.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>※ 목표 숫자는 영상 12~15개 × 질문 3~4개 기준입니다. 규모를 바꾸면 목표도 함께 조정하세요.</t>
         </is>

--- a/eval/labeling_sheet.xlsx
+++ b/eval/labeling_sheet.xlsx
@@ -5721,7 +5721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5948,12 +5948,12 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>uncSsiLbz1E</t>
+          <t>z8QPN-ITUvI</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>요리 레시피 쇼츠</t>
+          <t>도파민 터지는 참치비빔칼국수</t>
         </is>
       </c>
       <c r="D8" s="16" t="inlineStr">
@@ -5962,11 +5962,11 @@
         </is>
       </c>
       <c r="E8" s="15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=uncSsiLbz1E</t>
+          <t>https://www.youtube.com/watch?v=z8QPN-ITUvI</t>
         </is>
       </c>
       <c r="G8" s="15" t="inlineStr">
@@ -5986,12 +5986,12 @@
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>z8QPN-ITUvI</t>
+          <t>igP4-Rq5zgM</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>도파민 터지는 참치비빔칼국수</t>
+          <t>사리곰탕 파스타 #shorts #쇼츠 #사리곰탕면 #사리곰탕 #자취요리 #쉬운요리 #요리 #라면 #집밥요리 #간단한요리 #점심메뉴 #집밥 #사리곰탕파스타 #한국라면 #크림파스타</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
@@ -6000,11 +6000,11 @@
         </is>
       </c>
       <c r="E9" s="15" t="n">
-        <v>30</v>
+        <v>15.9</v>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=z8QPN-ITUvI</t>
+          <t>https://www.youtube.com/watch?v=igP4-Rq5zgM</t>
         </is>
       </c>
       <c r="G9" s="15" t="inlineStr">
@@ -6024,12 +6024,12 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>igP4-Rq5zgM</t>
+          <t>Zlo2JQzihwc</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>사리곰탕 파스타 #shorts #쇼츠 #사리곰탕면 #사리곰탕 #자취요리 #쉬운요리 #요리 #라면 #집밥요리 #간단한요리 #점심메뉴 #집밥 #사리곰탕파스타 #한국라면 #크림파스타</t>
+          <t>성시경이 감탄한 1등 레시피 미친 조합! #성시경 #라면레시피 #쇼츠</t>
         </is>
       </c>
       <c r="D10" s="16" t="inlineStr">
@@ -6038,11 +6038,11 @@
         </is>
       </c>
       <c r="E10" s="15" t="n">
-        <v>15.9</v>
+        <v>119.1</v>
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=igP4-Rq5zgM</t>
+          <t>https://www.youtube.com/watch?v=Zlo2JQzihwc</t>
         </is>
       </c>
       <c r="G10" s="15" t="inlineStr">
@@ -6062,25 +6062,25 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>Zlo2JQzihwc</t>
+          <t>5AP-rJGheKk</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>성시경이 감탄한 1등 레시피 미친 조합! #성시경 #라면레시피 #쇼츠</t>
+          <t>요리 레시피 쇼츠</t>
         </is>
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>후딱 레시피 Huttak</t>
         </is>
       </c>
       <c r="E11" s="15" t="n">
-        <v>119.1</v>
+        <v>45.6</v>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Zlo2JQzihwc</t>
+          <t>https://www.youtube.com/watch?v=5AP-rJGheKk</t>
         </is>
       </c>
       <c r="G11" s="15" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>5AP-rJGheKk</t>
+          <t>jPqpNbPT7yY</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>요리 레시피 쇼츠</t>
+          <t>명절 전부치기 동태전 혼자서도 쉽게 쉽게 노릇하고 바삭하게 #집밥 #제철음식 #cooking #레시피 #반찬 #food #shourt #쇼츠</t>
         </is>
       </c>
       <c r="D12" s="16" t="inlineStr">
@@ -6114,11 +6114,11 @@
         </is>
       </c>
       <c r="E12" s="15" t="n">
-        <v>45.6</v>
+        <v>33.5</v>
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5AP-rJGheKk</t>
+          <t>https://www.youtube.com/watch?v=jPqpNbPT7yY</t>
         </is>
       </c>
       <c r="G12" s="15" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>jPqpNbPT7yY</t>
+          <t>282ScDPvm28</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>명절 전부치기 동태전 혼자서도 쉽게 쉽게 노릇하고 바삭하게 #집밥 #제철음식 #cooking #레시피 #반찬 #food #shourt #쇼츠</t>
+          <t>짜장! 재료도 간단! 만들기도 간단! #shorts</t>
         </is>
       </c>
       <c r="D13" s="16" t="inlineStr">
@@ -6152,11 +6152,11 @@
         </is>
       </c>
       <c r="E13" s="15" t="n">
-        <v>33.5</v>
+        <v>30.9</v>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=jPqpNbPT7yY</t>
+          <t>https://www.youtube.com/watch?v=282ScDPvm28</t>
         </is>
       </c>
       <c r="G13" s="15" t="inlineStr">
@@ -6176,12 +6176,12 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>282ScDPvm28</t>
+          <t>sPeEcFdaD0M</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>짜장! 재료도 간단! 만들기도 간단! #shorts</t>
+          <t>너무 쉬워서 매일 먹는 두부 계란요리 Easy Tofu Egg Recipe</t>
         </is>
       </c>
       <c r="D14" s="16" t="inlineStr">
@@ -6190,11 +6190,11 @@
         </is>
       </c>
       <c r="E14" s="15" t="n">
-        <v>30.9</v>
+        <v>60</v>
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=282ScDPvm28</t>
+          <t>https://www.youtube.com/watch?v=sPeEcFdaD0M</t>
         </is>
       </c>
       <c r="G14" s="15" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>sPeEcFdaD0M</t>
+          <t>rfkc9X4BItc</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>너무 쉬워서 매일 먹는 두부 계란요리 Easy Tofu Egg Recipe</t>
+          <t>입맛 없을 때 무조건 해보세요! 오징어 초무침 황금 레시피 #간단요리 #반찬만들기 #오징어</t>
         </is>
       </c>
       <c r="D15" s="16" t="inlineStr">
@@ -6228,11 +6228,11 @@
         </is>
       </c>
       <c r="E15" s="15" t="n">
-        <v>60</v>
+        <v>61.5</v>
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=sPeEcFdaD0M</t>
+          <t>https://www.youtube.com/watch?v=rfkc9X4BItc</t>
         </is>
       </c>
       <c r="G15" s="15" t="inlineStr">
@@ -6252,12 +6252,12 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>rfkc9X4BItc</t>
+          <t>Hwzl8IA9NH0</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>입맛 없을 때 무조건 해보세요! 오징어 초무침 황금 레시피 #간단요리 #반찬만들기 #오징어</t>
+          <t>말도 안 되는 맛</t>
         </is>
       </c>
       <c r="D16" s="16" t="inlineStr">
@@ -6266,11 +6266,11 @@
         </is>
       </c>
       <c r="E16" s="15" t="n">
-        <v>61.5</v>
+        <v>27.9</v>
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rfkc9X4BItc</t>
+          <t>https://www.youtube.com/watch?v=Hwzl8IA9NH0</t>
         </is>
       </c>
       <c r="G16" s="15" t="inlineStr">
@@ -6290,12 +6290,12 @@
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>Hwzl8IA9NH0</t>
+          <t>11C8XqWobjQ</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>말도 안 되는 맛</t>
+          <t>[⭐️490만⭐️] 초간단 4분 잔치국수 뚝딱! #shorts</t>
         </is>
       </c>
       <c r="D17" s="16" t="inlineStr">
@@ -6304,11 +6304,11 @@
         </is>
       </c>
       <c r="E17" s="15" t="n">
-        <v>27.9</v>
+        <v>40.5</v>
       </c>
       <c r="F17" s="17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Hwzl8IA9NH0</t>
+          <t>https://www.youtube.com/watch?v=11C8XqWobjQ</t>
         </is>
       </c>
       <c r="G17" s="15" t="inlineStr">
@@ -6328,12 +6328,12 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>11C8XqWobjQ</t>
+          <t>iDMyw61V1XM</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>[⭐️490만⭐️] 초간단 4분 잔치국수 뚝딱! #shorts</t>
+          <t>지코바는 사 먹지 마세요!</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
@@ -6342,11 +6342,11 @@
         </is>
       </c>
       <c r="E18" s="15" t="n">
-        <v>40.5</v>
+        <v>55</v>
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=11C8XqWobjQ</t>
+          <t>https://www.youtube.com/watch?v=iDMyw61V1XM</t>
         </is>
       </c>
       <c r="G18" s="15" t="inlineStr">
@@ -6361,42 +6361,14 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>iDMyw61V1XM</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>지코바는 사 먹지 마세요!</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>후딱 레시피 Huttak</t>
-        </is>
-      </c>
-      <c r="E19" s="15" t="n">
-        <v>55</v>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=iDMyw61V1XM</t>
-        </is>
-      </c>
-      <c r="G19" s="15" t="inlineStr">
-        <is>
-          <t>ready</t>
-        </is>
-      </c>
-      <c r="H19" s="15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="A19" s="15" t="n"/>
+      <c r="B19" s="16" t="n"/>
+      <c r="C19" s="16" t="n"/>
+      <c r="D19" s="16" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="16" t="n"/>
+      <c r="G19" s="15" t="n"/>
+      <c r="H19" s="15" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="15" t="n"/>
@@ -6688,35 +6660,25 @@
       <c r="G48" s="15" t="n"/>
       <c r="H48" s="15" t="n"/>
     </row>
-    <row r="49">
-      <c r="A49" s="15" t="n"/>
-      <c r="B49" s="16" t="n"/>
-      <c r="C49" s="16" t="n"/>
-      <c r="D49" s="16" t="n"/>
-      <c r="E49" s="15" t="n"/>
-      <c r="F49" s="16" t="n"/>
-      <c r="G49" s="15" t="n"/>
-      <c r="H49" s="15" t="n"/>
+    <row r="50" ht="26" customHeight="1">
+      <c r="A50" s="18" t="inlineStr">
+        <is>
+          <t>· '질문 대상' 칸에 O 를 적은 영상에만 질문을 만듭니다. 저장 영상 25개 중 12~15개만 O 로 두고, 나머지는 검색 난이도를 유지하는 오답 후보로 남겨둡니다.</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="26" customHeight="1">
       <c r="A51" s="18" t="inlineStr">
         <is>
-          <t>· '질문 대상' 칸에 O 를 적은 영상에만 질문을 만듭니다. 저장 영상 25개 중 12~15개만 O 로 두고, 나머지는 검색 난이도를 유지하는 오답 후보로 남겨둡니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="26" customHeight="1">
-      <c r="A52" s="18" t="inlineStr">
-        <is>
           <t>· 상태가 ready 가 아닌 영상은 분석이 끝나지 않은 것입니다. 질문 대상에서 제외하세요.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A50:H50"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A51:H51"/>
-    <mergeCell ref="A52:H52"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -6735,7 +6697,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/eval/labeling_sheet.xlsx
+++ b/eval/labeling_sheet.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -85,8 +85,12 @@
       <color rgb="001F3864"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -106,6 +110,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF7E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -135,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -195,6 +204,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1177,8 +1198,8 @@
   <mergeCells count="44">
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="B14:D14"/>
-    <mergeCell ref="C24:D24"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="B60:D60"/>
@@ -1230,7 +1251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I399"/>
+  <dimension ref="A1:I398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1287,1282 +1308,4816 @@
       </c>
       <c r="I1" s="9" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>source</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>q01</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>PbCq-C9GRzs</t>
-        </is>
-      </c>
-      <c r="C2" s="13" t="inlineStr">
-        <is>
-          <t>가지는 어떻게 썰어?</t>
-        </is>
-      </c>
-      <c r="D2" s="12" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>q001</t>
+        </is>
+      </c>
+      <c r="B2" s="22" t="inlineStr">
+        <is>
+          <t>rfkc9X4BItc</t>
+        </is>
+      </c>
+      <c r="C2" s="22" t="inlineStr">
+        <is>
+          <t>처음에 물은 얼마나 넣어?</t>
+        </is>
+      </c>
+      <c r="D2" s="21" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E2" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="F2" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="G2" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H2" s="22" t="inlineStr">
+        <is>
+          <t>임준서</t>
+        </is>
+      </c>
+      <c r="I2" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>q001</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>rfkc9X4BItc</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>처음에 물은 얼마나 넣어?</t>
+        </is>
+      </c>
+      <c r="D3" s="23" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E3" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="F3" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="G3" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H3" s="24" t="inlineStr">
+        <is>
+          <t>임준서</t>
+        </is>
+      </c>
+      <c r="I3" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>q002</t>
+        </is>
+      </c>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>rfkc9X4BItc</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>오징어는 언제 넣어?</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t>순서타이밍</t>
         </is>
       </c>
-      <c r="E2" s="12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F2" s="12" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G2" s="12" t="n">
+      <c r="E4" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="F4" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="G4" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="22" t="inlineStr">
+        <is>
+          <t>임준서</t>
+        </is>
+      </c>
+      <c r="I4" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>q002</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>rfkc9X4BItc</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>오징어는 언제 넣어?</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E5" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="G5" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H5" s="24" t="inlineStr">
+        <is>
+          <t>임준서</t>
+        </is>
+      </c>
+      <c r="I5" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>q003</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>rfkc9X4BItc</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>무는 어느 정도로 썰어?</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>시각적상태</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="F6" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>임준서</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>q003</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>rfkc9X4BItc</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>무는 어느 정도로 썰어?</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>시각적상태</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="n">
+        <v>18</v>
+      </c>
+      <c r="F7" s="23" t="n">
+        <v>22</v>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="24" t="inlineStr">
+        <is>
+          <t>임준서</t>
+        </is>
+      </c>
+      <c r="I7" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>q004</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>rfkc9X4BItc</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>맛술은 얼마나 넣어?</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="n"/>
+      <c r="F8" s="21" t="n"/>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>임준서</t>
+        </is>
+      </c>
+      <c r="I8" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>q005</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>Hwzl8IA9NH0</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>새우는 언제까지 볶아야해?</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>시각적상태</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="F9" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>임준서</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>q005</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>Hwzl8IA9NH0</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>새우는 언제까지 볶아야해?</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>시각적상태</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="F10" s="23" t="n">
+        <v>13</v>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>임준서</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>q006</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>Hwzl8IA9NH0</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>새우는 얼마나 넣어?</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>임준서</t>
+        </is>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>q006</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>Hwzl8IA9NH0</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>새우는 얼마나 넣어?</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>임준서</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>q007</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>Hwzl8IA9NH0</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>토마토소스는 얼마나 넣어?</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="F13" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t>임준서</t>
+        </is>
+      </c>
+      <c r="I13" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>q007</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>Hwzl8IA9NH0</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>토마토소스는 얼마나 넣어?</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="F14" s="23" t="n">
+        <v>20</v>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>임준서</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>q008</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>Hwzl8IA9NH0</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>간장은 몇 스푼 넣어?</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="n"/>
+      <c r="F15" s="21" t="n"/>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>임준서</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>q009</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>11C8XqWobjQ</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>양념에 들어가는 재료들은 뭐야?</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="F16" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>임준서</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>q009</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>11C8XqWobjQ</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>양념에 들어가는 재료들은 뭐야?</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="F17" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="G17" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>임준서</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>q010</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>11C8XqWobjQ</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>멸치육수는 얼마나 넣어?</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="F18" s="21" t="n">
+        <v>29</v>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>임준서</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>q010</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>11C8XqWobjQ</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>멸치육수는 얼마나 넣어?</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="n">
+        <v>21</v>
+      </c>
+      <c r="F19" s="23" t="n">
+        <v>25</v>
+      </c>
+      <c r="G19" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>임준서</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>q011</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>11C8XqWobjQ</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>당근이랑 애호박은 어떻게 썰어?</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>시각적상태</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F20" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>임준서</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>q011</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>11C8XqWobjQ</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>당근이랑 애호박은 어떻게 썰어?</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>시각적상태</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F21" s="23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>임준서</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>q012</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>11C8XqWobjQ</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>김치는 언제 넣어?</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="n"/>
+      <c r="F22" s="21" t="n"/>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>임준서</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>q013</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>iDMyw61V1XM</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>양념장에 어떤 재료들 들어가?</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="F23" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>임준서</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>q013</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>iDMyw61V1XM</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>양념장에 어떤 재료들 들어가?</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F24" s="23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G24" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>임준서</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>q014</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>iDMyw61V1XM</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>떡은 언제 넣어?</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="F25" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>임준서</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>q014</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>iDMyw61V1XM</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>떡은 언제 넣어?</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="n">
+        <v>27</v>
+      </c>
+      <c r="F26" s="23" t="n">
+        <v>31</v>
+      </c>
+      <c r="G26" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>임준서</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>q015</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>iDMyw61V1XM</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>양념은 어느 정도로 졸여?</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>시각적상태</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="n">
+        <v>43</v>
+      </c>
+      <c r="F27" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
+        <is>
+          <t>임준서</t>
+        </is>
+      </c>
+      <c r="I27" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>q015</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>iDMyw61V1XM</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>양념은 어느 정도로 졸여?</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr">
+        <is>
+          <t>시각적상태</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="n">
+        <v>39</v>
+      </c>
+      <c r="F28" s="23" t="n">
+        <v>43</v>
+      </c>
+      <c r="G28" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
+        <is>
+          <t>임준서</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>q016</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>iDMyw61V1XM</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>오븐에는 몇 분 구워?</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="n"/>
+      <c r="F29" s="21" t="n"/>
+      <c r="G29" s="21" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H29" s="22" t="inlineStr">
+        <is>
+          <t>임준서</t>
+        </is>
+      </c>
+      <c r="I29" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>q017</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>l3WthBEFzFw</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>양파가 몇 개나 들어가?</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F30" s="21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H30" s="22" t="inlineStr">
+        <is>
+          <t>이동현</t>
+        </is>
+      </c>
+      <c r="I30" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>q017</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>l3WthBEFzFw</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>양파가 몇 개나 들어가?</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F31" s="23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G31" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H31" s="24" t="inlineStr">
+        <is>
+          <t>이동현</t>
+        </is>
+      </c>
+      <c r="I31" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>q018</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>l3WthBEFzFw</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>감자랑 양파 볶고 나서 다음에 뭐해야 되지?</t>
+        </is>
+      </c>
+      <c r="D32" s="21" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E32" s="21" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="F32" s="21" t="n">
+        <v>39</v>
+      </c>
+      <c r="G32" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H32" s="22" t="inlineStr">
+        <is>
+          <t>이동현</t>
+        </is>
+      </c>
+      <c r="I32" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="23" t="inlineStr">
+        <is>
+          <t>q018</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>l3WthBEFzFw</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>감자랑 양파 볶고 나서 다음에 뭐해야 되지?</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E33" s="23" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="F33" s="23" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="G33" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H33" s="24" t="inlineStr">
+        <is>
+          <t>이동현</t>
+        </is>
+      </c>
+      <c r="I33" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>q019</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>l3WthBEFzFw</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>간장 넣는 장면 찾아줘</t>
+        </is>
+      </c>
+      <c r="D34" s="21" t="inlineStr">
+        <is>
+          <t>시각적상태</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="F34" s="21" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="G34" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H34" s="22" t="inlineStr">
+        <is>
+          <t>이동현</t>
+        </is>
+      </c>
+      <c r="I34" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>q019</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>l3WthBEFzFw</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>간장 넣는 장면 찾아줘</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="inlineStr">
+        <is>
+          <t>시각적상태</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="F35" s="23" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="G35" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H35" s="24" t="inlineStr">
+        <is>
+          <t>이동현</t>
+        </is>
+      </c>
+      <c r="I35" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="21" t="inlineStr">
+        <is>
+          <t>q020</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>l3WthBEFzFw</t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>당근 넣는 장면 찾아줘</t>
+        </is>
+      </c>
+      <c r="D36" s="21" t="inlineStr">
+        <is>
+          <t>시각적상태</t>
+        </is>
+      </c>
+      <c r="E36" s="21" t="n"/>
+      <c r="F36" s="21" t="n"/>
+      <c r="G36" s="21" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H36" s="22" t="inlineStr">
+        <is>
+          <t>이동현</t>
+        </is>
+      </c>
+      <c r="I36" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="21" t="inlineStr">
+        <is>
+          <t>q021</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>z8QPN-ITUvI</t>
+        </is>
+      </c>
+      <c r="C37" s="22" t="inlineStr">
+        <is>
+          <t>식초 몇 스푼 들어가지?</t>
+        </is>
+      </c>
+      <c r="D37" s="21" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E37" s="21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="F37" s="21" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="G37" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H37" s="22" t="inlineStr">
+        <is>
+          <t>이동현</t>
+        </is>
+      </c>
+      <c r="I37" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="23" t="inlineStr">
+        <is>
+          <t>q021</t>
+        </is>
+      </c>
+      <c r="B38" s="24" t="inlineStr">
+        <is>
+          <t>z8QPN-ITUvI</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
+        <is>
+          <t>식초 몇 스푼 들어가지?</t>
+        </is>
+      </c>
+      <c r="D38" s="23" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E38" s="23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F38" s="23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G38" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H38" s="24" t="inlineStr">
+        <is>
+          <t>이동현</t>
+        </is>
+      </c>
+      <c r="I38" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="21" t="inlineStr">
+        <is>
+          <t>q022</t>
+        </is>
+      </c>
+      <c r="B39" s="22" t="inlineStr">
+        <is>
+          <t>z8QPN-ITUvI</t>
+        </is>
+      </c>
+      <c r="C39" s="22" t="inlineStr">
+        <is>
+          <t>양념장에 면 넣고나서 뭐해야되지?</t>
+        </is>
+      </c>
+      <c r="D39" s="21" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E39" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="F39" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="G39" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H39" s="22" t="inlineStr">
+        <is>
+          <t>이동현</t>
+        </is>
+      </c>
+      <c r="I39" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="23" t="inlineStr">
+        <is>
+          <t>q022</t>
+        </is>
+      </c>
+      <c r="B40" s="24" t="inlineStr">
+        <is>
+          <t>z8QPN-ITUvI</t>
+        </is>
+      </c>
+      <c r="C40" s="24" t="inlineStr">
+        <is>
+          <t>양념장에 면 넣고나서 뭐해야되지?</t>
+        </is>
+      </c>
+      <c r="D40" s="23" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E40" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="F40" s="23" t="n">
+        <v>20</v>
+      </c>
+      <c r="G40" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H40" s="24" t="inlineStr">
+        <is>
+          <t>이동현</t>
+        </is>
+      </c>
+      <c r="I40" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="21" t="inlineStr">
+        <is>
+          <t>q023</t>
+        </is>
+      </c>
+      <c r="B41" s="22" t="inlineStr">
+        <is>
+          <t>z8QPN-ITUvI</t>
+        </is>
+      </c>
+      <c r="C41" s="22" t="inlineStr">
+        <is>
+          <t>상추 찢어서 넣는 장면 찾아줘</t>
+        </is>
+      </c>
+      <c r="D41" s="21" t="inlineStr">
+        <is>
+          <t>시각적상태</t>
+        </is>
+      </c>
+      <c r="E41" s="21" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="F41" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="G41" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H41" s="22" t="inlineStr">
+        <is>
+          <t>이동현</t>
+        </is>
+      </c>
+      <c r="I41" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="23" t="inlineStr">
+        <is>
+          <t>q023</t>
+        </is>
+      </c>
+      <c r="B42" s="24" t="inlineStr">
+        <is>
+          <t>z8QPN-ITUvI</t>
+        </is>
+      </c>
+      <c r="C42" s="24" t="inlineStr">
+        <is>
+          <t>상추 찢어서 넣는 장면 찾아줘</t>
+        </is>
+      </c>
+      <c r="D42" s="23" t="inlineStr">
+        <is>
+          <t>시각적상태</t>
+        </is>
+      </c>
+      <c r="E42" s="23" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F42" s="23" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="G42" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H42" s="24" t="inlineStr">
+        <is>
+          <t>이동현</t>
+        </is>
+      </c>
+      <c r="I42" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="21" t="inlineStr">
+        <is>
+          <t>q024</t>
+        </is>
+      </c>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>z8QPN-ITUvI</t>
+        </is>
+      </c>
+      <c r="C43" s="22" t="inlineStr">
+        <is>
+          <t>반죽 잘라서 면 만드는 과정 찾아줘</t>
+        </is>
+      </c>
+      <c r="D43" s="21" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H43" s="22" t="inlineStr">
+        <is>
+          <t>이동현</t>
+        </is>
+      </c>
+      <c r="I43" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="21" t="inlineStr">
+        <is>
+          <t>q025</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>igP4-Rq5zgM</t>
+        </is>
+      </c>
+      <c r="C44" s="22" t="inlineStr">
+        <is>
+          <t>사리곰탕 스프 얼마나 들어가지?</t>
+        </is>
+      </c>
+      <c r="D44" s="21" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E44" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F44" s="21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G44" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H44" s="22" t="inlineStr">
+        <is>
+          <t>이동현</t>
+        </is>
+      </c>
+      <c r="I44" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="23" t="inlineStr">
+        <is>
+          <t>q025</t>
+        </is>
+      </c>
+      <c r="B45" s="24" t="inlineStr">
+        <is>
+          <t>igP4-Rq5zgM</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="inlineStr">
+        <is>
+          <t>사리곰탕 스프 얼마나 들어가지?</t>
+        </is>
+      </c>
+      <c r="D45" s="23" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E45" s="23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F45" s="23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G45" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H45" s="24" t="inlineStr">
+        <is>
+          <t>이동현</t>
+        </is>
+      </c>
+      <c r="I45" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="21" t="inlineStr">
+        <is>
+          <t>q026</t>
+        </is>
+      </c>
+      <c r="B46" s="22" t="inlineStr">
+        <is>
+          <t>igP4-Rq5zgM</t>
+        </is>
+      </c>
+      <c r="C46" s="22" t="inlineStr">
+        <is>
+          <t>다진 마늘 넣고 나서 뭐 넣어야되지?</t>
+        </is>
+      </c>
+      <c r="D46" s="21" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E46" s="21" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F46" s="21" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G46" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H46" s="22" t="inlineStr">
+        <is>
+          <t>이동현</t>
+        </is>
+      </c>
+      <c r="I46" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="23" t="inlineStr">
+        <is>
+          <t>q026</t>
+        </is>
+      </c>
+      <c r="B47" s="24" t="inlineStr">
+        <is>
+          <t>igP4-Rq5zgM</t>
+        </is>
+      </c>
+      <c r="C47" s="24" t="inlineStr">
+        <is>
+          <t>다진 마늘 넣고 나서 뭐 넣어야되지?</t>
+        </is>
+      </c>
+      <c r="D47" s="23" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E47" s="23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F47" s="23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G47" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H47" s="24" t="inlineStr">
+        <is>
+          <t>이동현</t>
+        </is>
+      </c>
+      <c r="I47" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="21" t="inlineStr">
+        <is>
+          <t>q027</t>
+        </is>
+      </c>
+      <c r="B48" s="22" t="inlineStr">
+        <is>
+          <t>igP4-Rq5zgM</t>
+        </is>
+      </c>
+      <c r="C48" s="22" t="inlineStr">
+        <is>
+          <t>후추 뿌리는 장면 찾아줘</t>
+        </is>
+      </c>
+      <c r="D48" s="21" t="inlineStr">
+        <is>
+          <t>시각적상태</t>
+        </is>
+      </c>
+      <c r="E48" s="21" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="F48" s="21" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="G48" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H48" s="22" t="inlineStr">
+        <is>
+          <t>이동현</t>
+        </is>
+      </c>
+      <c r="I48" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="23" t="inlineStr">
+        <is>
+          <t>q027</t>
+        </is>
+      </c>
+      <c r="B49" s="24" t="inlineStr">
+        <is>
+          <t>igP4-Rq5zgM</t>
+        </is>
+      </c>
+      <c r="C49" s="24" t="inlineStr">
+        <is>
+          <t>후추 뿌리는 장면 찾아줘</t>
+        </is>
+      </c>
+      <c r="D49" s="23" t="inlineStr">
+        <is>
+          <t>시각적상태</t>
+        </is>
+      </c>
+      <c r="E49" s="23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F49" s="23" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="G49" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H49" s="24" t="inlineStr">
+        <is>
+          <t>이동현</t>
+        </is>
+      </c>
+      <c r="I49" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="21" t="inlineStr">
+        <is>
+          <t>q028</t>
+        </is>
+      </c>
+      <c r="B50" s="22" t="inlineStr">
+        <is>
+          <t>igP4-Rq5zgM</t>
+        </is>
+      </c>
+      <c r="C50" s="22" t="inlineStr">
+        <is>
+          <t>고추장 넣는 장면이 몇 초에 있더라?</t>
+        </is>
+      </c>
+      <c r="D50" s="21" t="inlineStr">
+        <is>
+          <t>시각적상태</t>
+        </is>
+      </c>
+      <c r="E50" s="21" t="n"/>
+      <c r="F50" s="21" t="n"/>
+      <c r="G50" s="21" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H50" s="22" t="inlineStr">
+        <is>
+          <t>이동현</t>
+        </is>
+      </c>
+      <c r="I50" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="21" t="inlineStr">
+        <is>
+          <t>q029</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>Zlo2JQzihwc</t>
+        </is>
+      </c>
+      <c r="C51" s="22" t="inlineStr">
+        <is>
+          <t>짜파게티 면이 몇개나 들어가지?</t>
+        </is>
+      </c>
+      <c r="D51" s="21" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E51" s="21" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F51" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="G51" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H51" s="22" t="inlineStr">
+        <is>
+          <t>이동현</t>
+        </is>
+      </c>
+      <c r="I51" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="23" t="inlineStr">
+        <is>
+          <t>q029</t>
+        </is>
+      </c>
+      <c r="B52" s="24" t="inlineStr">
+        <is>
+          <t>Zlo2JQzihwc</t>
+        </is>
+      </c>
+      <c r="C52" s="24" t="inlineStr">
+        <is>
+          <t>짜파게티 면이 몇개나 들어가지?</t>
+        </is>
+      </c>
+      <c r="D52" s="23" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E52" s="23" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F52" s="23" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G52" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H52" s="24" t="inlineStr">
+        <is>
+          <t>이동현</t>
+        </is>
+      </c>
+      <c r="I52" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="21" t="inlineStr">
+        <is>
+          <t>q030</t>
+        </is>
+      </c>
+      <c r="B53" s="22" t="inlineStr">
+        <is>
+          <t>Zlo2JQzihwc</t>
+        </is>
+      </c>
+      <c r="C53" s="22" t="inlineStr">
+        <is>
+          <t>새우 넣고 소금 후추 간 하는게 몇 초였지?</t>
+        </is>
+      </c>
+      <c r="D53" s="21" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E53" s="21" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="F53" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="G53" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H53" s="22" t="inlineStr">
+        <is>
+          <t>이동현</t>
+        </is>
+      </c>
+      <c r="I53" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="23" t="inlineStr">
+        <is>
+          <t>q030</t>
+        </is>
+      </c>
+      <c r="B54" s="24" t="inlineStr">
+        <is>
+          <t>Zlo2JQzihwc</t>
+        </is>
+      </c>
+      <c r="C54" s="24" t="inlineStr">
+        <is>
+          <t>새우 넣고 소금 후추 간 하는게 몇 초였지?</t>
+        </is>
+      </c>
+      <c r="D54" s="23" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E54" s="23" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F54" s="23" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="G54" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H54" s="24" t="inlineStr">
+        <is>
+          <t>이동현</t>
+        </is>
+      </c>
+      <c r="I54" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="21" t="inlineStr">
+        <is>
+          <t>q031</t>
+        </is>
+      </c>
+      <c r="B55" s="22" t="inlineStr">
+        <is>
+          <t>Zlo2JQzihwc</t>
+        </is>
+      </c>
+      <c r="C55" s="22" t="inlineStr">
+        <is>
+          <t>익힌 면 건져넣는 장면 찾아줘</t>
+        </is>
+      </c>
+      <c r="D55" s="21" t="inlineStr">
+        <is>
+          <t>시각적상태</t>
+        </is>
+      </c>
+      <c r="E55" s="21" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="F55" s="21" t="n">
+        <v>43</v>
+      </c>
+      <c r="G55" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H55" s="22" t="inlineStr">
+        <is>
+          <t>이동현</t>
+        </is>
+      </c>
+      <c r="I55" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="23" t="inlineStr">
+        <is>
+          <t>q031</t>
+        </is>
+      </c>
+      <c r="B56" s="24" t="inlineStr">
+        <is>
+          <t>Zlo2JQzihwc</t>
+        </is>
+      </c>
+      <c r="C56" s="24" t="inlineStr">
+        <is>
+          <t>익힌 면 건져넣는 장면 찾아줘</t>
+        </is>
+      </c>
+      <c r="D56" s="23" t="inlineStr">
+        <is>
+          <t>시각적상태</t>
+        </is>
+      </c>
+      <c r="E56" s="23" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="F56" s="23" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="G56" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H56" s="24" t="inlineStr">
+        <is>
+          <t>이동현</t>
+        </is>
+      </c>
+      <c r="I56" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="21" t="inlineStr">
+        <is>
+          <t>q032</t>
+        </is>
+      </c>
+      <c r="B57" s="22" t="inlineStr">
+        <is>
+          <t>Zlo2JQzihwc</t>
+        </is>
+      </c>
+      <c r="C57" s="22" t="inlineStr">
+        <is>
+          <t>성시경이 맥주 같이 먹는 장면 찾아줘</t>
+        </is>
+      </c>
+      <c r="D57" s="21" t="inlineStr">
+        <is>
+          <t>시각적상태</t>
+        </is>
+      </c>
+      <c r="E57" s="21" t="n"/>
+      <c r="F57" s="21" t="n"/>
+      <c r="G57" s="21" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H57" s="22" t="inlineStr">
+        <is>
+          <t>이동현</t>
+        </is>
+      </c>
+      <c r="I57" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="21" t="inlineStr">
+        <is>
+          <t>q033</t>
+        </is>
+      </c>
+      <c r="B58" s="22" t="inlineStr">
+        <is>
+          <t>SggDZVu0DPk</t>
+        </is>
+      </c>
+      <c r="C58" s="22" t="inlineStr">
+        <is>
+          <t>양념 넣는 부분 보여줘</t>
+        </is>
+      </c>
+      <c r="D58" s="21" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E58" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="F58" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="G58" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H58" s="22" t="inlineStr">
+        <is>
+          <t>박현준</t>
+        </is>
+      </c>
+      <c r="I58" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="23" t="inlineStr">
+        <is>
+          <t>q033</t>
+        </is>
+      </c>
+      <c r="B59" s="24" t="inlineStr">
+        <is>
+          <t>SggDZVu0DPk</t>
+        </is>
+      </c>
+      <c r="C59" s="24" t="inlineStr">
+        <is>
+          <t>양념 넣는 부분 보여줘</t>
+        </is>
+      </c>
+      <c r="D59" s="23" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E59" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="F59" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="G59" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H59" s="24" t="inlineStr">
+        <is>
+          <t>박현준</t>
+        </is>
+      </c>
+      <c r="I59" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="21" t="inlineStr">
+        <is>
+          <t>q034</t>
+        </is>
+      </c>
+      <c r="B60" s="22" t="inlineStr">
+        <is>
+          <t>SggDZVu0DPk</t>
+        </is>
+      </c>
+      <c r="C60" s="22" t="inlineStr">
+        <is>
+          <t>음식이 완성된 부분 보여줘</t>
+        </is>
+      </c>
+      <c r="D60" s="21" t="inlineStr">
+        <is>
+          <t>시각적상태</t>
+        </is>
+      </c>
+      <c r="E60" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="F60" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="G60" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H60" s="22" t="inlineStr">
+        <is>
+          <t>박현준</t>
+        </is>
+      </c>
+      <c r="I60" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="23" t="inlineStr">
+        <is>
+          <t>q034</t>
+        </is>
+      </c>
+      <c r="B61" s="24" t="inlineStr">
+        <is>
+          <t>SggDZVu0DPk</t>
+        </is>
+      </c>
+      <c r="C61" s="24" t="inlineStr">
+        <is>
+          <t>음식이 완성된 부분 보여줘</t>
+        </is>
+      </c>
+      <c r="D61" s="23" t="inlineStr">
+        <is>
+          <t>시각적상태</t>
+        </is>
+      </c>
+      <c r="E61" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="F61" s="23" t="n">
+        <v>15</v>
+      </c>
+      <c r="G61" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H61" s="24" t="inlineStr">
+        <is>
+          <t>박현준</t>
+        </is>
+      </c>
+      <c r="I61" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="21" t="inlineStr">
+        <is>
+          <t>q035</t>
+        </is>
+      </c>
+      <c r="B62" s="22" t="inlineStr">
+        <is>
+          <t>SggDZVu0DPk</t>
+        </is>
+      </c>
+      <c r="C62" s="22" t="inlineStr">
+        <is>
+          <t>물은 얼마나 넣어?</t>
+        </is>
+      </c>
+      <c r="D62" s="21" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E62" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="F62" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="G62" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H62" s="22" t="inlineStr">
+        <is>
+          <t>박현준</t>
+        </is>
+      </c>
+      <c r="I62" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="23" t="inlineStr">
+        <is>
+          <t>q035</t>
+        </is>
+      </c>
+      <c r="B63" s="24" t="inlineStr">
+        <is>
+          <t>SggDZVu0DPk</t>
+        </is>
+      </c>
+      <c r="C63" s="24" t="inlineStr">
+        <is>
+          <t>물은 얼마나 넣어?</t>
+        </is>
+      </c>
+      <c r="D63" s="23" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E63" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="H2" s="13" t="inlineStr">
-        <is>
-          <t>예시-지우세요</t>
-        </is>
-      </c>
-      <c r="I2" s="14" t="inlineStr">
-        <is>
-          <t>← 이 줄은 예시입니다. 확인 후 행 전체를 삭제하고 3행부터 쓰세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="15" t="n"/>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="15" t="n"/>
-      <c r="E3" s="15" t="n"/>
-      <c r="F3" s="15" t="n"/>
-      <c r="G3" s="15" t="n"/>
-      <c r="H3" s="16" t="n"/>
-      <c r="I3" s="16" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="15" t="n"/>
-      <c r="B4" s="16" t="n"/>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="15" t="n"/>
-      <c r="E4" s="15" t="n"/>
-      <c r="F4" s="15" t="n"/>
-      <c r="G4" s="15" t="n"/>
-      <c r="H4" s="16" t="n"/>
-      <c r="I4" s="16" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="15" t="n"/>
-      <c r="B5" s="16" t="n"/>
-      <c r="C5" s="16" t="n"/>
-      <c r="D5" s="15" t="n"/>
-      <c r="E5" s="15" t="n"/>
-      <c r="F5" s="15" t="n"/>
-      <c r="G5" s="15" t="n"/>
-      <c r="H5" s="16" t="n"/>
-      <c r="I5" s="16" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="n"/>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="15" t="n"/>
-      <c r="E6" s="15" t="n"/>
-      <c r="F6" s="15" t="n"/>
-      <c r="G6" s="15" t="n"/>
-      <c r="H6" s="16" t="n"/>
-      <c r="I6" s="16" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="n"/>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="15" t="n"/>
-      <c r="E7" s="15" t="n"/>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
-      <c r="H7" s="16" t="n"/>
-      <c r="I7" s="16" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="n"/>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="16" t="n"/>
-      <c r="D8" s="15" t="n"/>
-      <c r="E8" s="15" t="n"/>
-      <c r="F8" s="15" t="n"/>
-      <c r="G8" s="15" t="n"/>
-      <c r="H8" s="16" t="n"/>
-      <c r="I8" s="16" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="15" t="n"/>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="15" t="n"/>
-      <c r="E9" s="15" t="n"/>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
-      <c r="H9" s="16" t="n"/>
-      <c r="I9" s="16" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="n"/>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="15" t="n"/>
-      <c r="E10" s="15" t="n"/>
-      <c r="F10" s="15" t="n"/>
-      <c r="G10" s="15" t="n"/>
-      <c r="H10" s="16" t="n"/>
-      <c r="I10" s="16" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="n"/>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="16" t="n"/>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="15" t="n"/>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
-      <c r="H11" s="16" t="n"/>
-      <c r="I11" s="16" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="n"/>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="15" t="n"/>
-      <c r="F12" s="15" t="n"/>
-      <c r="G12" s="15" t="n"/>
-      <c r="H12" s="16" t="n"/>
-      <c r="I12" s="16" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="n"/>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="15" t="n"/>
-      <c r="E13" s="15" t="n"/>
-      <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
-      <c r="H13" s="16" t="n"/>
-      <c r="I13" s="16" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="15" t="n"/>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="15" t="n"/>
-      <c r="E14" s="15" t="n"/>
-      <c r="F14" s="15" t="n"/>
-      <c r="G14" s="15" t="n"/>
-      <c r="H14" s="16" t="n"/>
-      <c r="I14" s="16" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="n"/>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="16" t="n"/>
-      <c r="D15" s="15" t="n"/>
-      <c r="E15" s="15" t="n"/>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
-      <c r="H15" s="16" t="n"/>
-      <c r="I15" s="16" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="n"/>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="16" t="n"/>
-      <c r="D16" s="15" t="n"/>
-      <c r="E16" s="15" t="n"/>
-      <c r="F16" s="15" t="n"/>
-      <c r="G16" s="15" t="n"/>
-      <c r="H16" s="16" t="n"/>
-      <c r="I16" s="16" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="n"/>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="15" t="n"/>
-      <c r="E17" s="15" t="n"/>
-      <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
-      <c r="H17" s="16" t="n"/>
-      <c r="I17" s="16" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="n"/>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="15" t="n"/>
-      <c r="E18" s="15" t="n"/>
-      <c r="F18" s="15" t="n"/>
-      <c r="G18" s="15" t="n"/>
-      <c r="H18" s="16" t="n"/>
-      <c r="I18" s="16" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="n"/>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="16" t="n"/>
-      <c r="D19" s="15" t="n"/>
-      <c r="E19" s="15" t="n"/>
-      <c r="F19" s="15" t="n"/>
-      <c r="G19" s="15" t="n"/>
-      <c r="H19" s="16" t="n"/>
-      <c r="I19" s="16" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="n"/>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="15" t="n"/>
-      <c r="E20" s="15" t="n"/>
-      <c r="F20" s="15" t="n"/>
-      <c r="G20" s="15" t="n"/>
-      <c r="H20" s="16" t="n"/>
-      <c r="I20" s="16" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="n"/>
-      <c r="B21" s="16" t="n"/>
-      <c r="C21" s="16" t="n"/>
-      <c r="D21" s="15" t="n"/>
-      <c r="E21" s="15" t="n"/>
-      <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
-      <c r="H21" s="16" t="n"/>
-      <c r="I21" s="16" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="n"/>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="15" t="n"/>
-      <c r="E22" s="15" t="n"/>
-      <c r="F22" s="15" t="n"/>
-      <c r="G22" s="15" t="n"/>
-      <c r="H22" s="16" t="n"/>
-      <c r="I22" s="16" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="n"/>
-      <c r="B23" s="16" t="n"/>
-      <c r="C23" s="16" t="n"/>
-      <c r="D23" s="15" t="n"/>
-      <c r="E23" s="15" t="n"/>
-      <c r="F23" s="15" t="n"/>
-      <c r="G23" s="15" t="n"/>
-      <c r="H23" s="16" t="n"/>
-      <c r="I23" s="16" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="n"/>
-      <c r="B24" s="16" t="n"/>
-      <c r="C24" s="16" t="n"/>
-      <c r="D24" s="15" t="n"/>
-      <c r="E24" s="15" t="n"/>
-      <c r="F24" s="15" t="n"/>
-      <c r="G24" s="15" t="n"/>
-      <c r="H24" s="16" t="n"/>
-      <c r="I24" s="16" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="15" t="n"/>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="15" t="n"/>
-      <c r="E25" s="15" t="n"/>
-      <c r="F25" s="15" t="n"/>
-      <c r="G25" s="15" t="n"/>
-      <c r="H25" s="16" t="n"/>
-      <c r="I25" s="16" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="n"/>
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="16" t="n"/>
-      <c r="D26" s="15" t="n"/>
-      <c r="E26" s="15" t="n"/>
-      <c r="F26" s="15" t="n"/>
-      <c r="G26" s="15" t="n"/>
-      <c r="H26" s="16" t="n"/>
-      <c r="I26" s="16" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="n"/>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="15" t="n"/>
-      <c r="E27" s="15" t="n"/>
-      <c r="F27" s="15" t="n"/>
-      <c r="G27" s="15" t="n"/>
-      <c r="H27" s="16" t="n"/>
-      <c r="I27" s="16" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="15" t="n"/>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="15" t="n"/>
-      <c r="E28" s="15" t="n"/>
-      <c r="F28" s="15" t="n"/>
-      <c r="G28" s="15" t="n"/>
-      <c r="H28" s="16" t="n"/>
-      <c r="I28" s="16" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="15" t="n"/>
-      <c r="B29" s="16" t="n"/>
-      <c r="C29" s="16" t="n"/>
-      <c r="D29" s="15" t="n"/>
-      <c r="E29" s="15" t="n"/>
-      <c r="F29" s="15" t="n"/>
-      <c r="G29" s="15" t="n"/>
-      <c r="H29" s="16" t="n"/>
-      <c r="I29" s="16" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="n"/>
-      <c r="B30" s="16" t="n"/>
-      <c r="C30" s="16" t="n"/>
-      <c r="D30" s="15" t="n"/>
-      <c r="E30" s="15" t="n"/>
-      <c r="F30" s="15" t="n"/>
-      <c r="G30" s="15" t="n"/>
-      <c r="H30" s="16" t="n"/>
-      <c r="I30" s="16" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="15" t="n"/>
-      <c r="B31" s="16" t="n"/>
-      <c r="C31" s="16" t="n"/>
-      <c r="D31" s="15" t="n"/>
-      <c r="E31" s="15" t="n"/>
-      <c r="F31" s="15" t="n"/>
-      <c r="G31" s="15" t="n"/>
-      <c r="H31" s="16" t="n"/>
-      <c r="I31" s="16" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="n"/>
-      <c r="B32" s="16" t="n"/>
-      <c r="C32" s="16" t="n"/>
-      <c r="D32" s="15" t="n"/>
-      <c r="E32" s="15" t="n"/>
-      <c r="F32" s="15" t="n"/>
-      <c r="G32" s="15" t="n"/>
-      <c r="H32" s="16" t="n"/>
-      <c r="I32" s="16" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="n"/>
-      <c r="B33" s="16" t="n"/>
-      <c r="C33" s="16" t="n"/>
-      <c r="D33" s="15" t="n"/>
-      <c r="E33" s="15" t="n"/>
-      <c r="F33" s="15" t="n"/>
-      <c r="G33" s="15" t="n"/>
-      <c r="H33" s="16" t="n"/>
-      <c r="I33" s="16" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="n"/>
-      <c r="B34" s="16" t="n"/>
-      <c r="C34" s="16" t="n"/>
-      <c r="D34" s="15" t="n"/>
-      <c r="E34" s="15" t="n"/>
-      <c r="F34" s="15" t="n"/>
-      <c r="G34" s="15" t="n"/>
-      <c r="H34" s="16" t="n"/>
-      <c r="I34" s="16" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="15" t="n"/>
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="15" t="n"/>
-      <c r="E35" s="15" t="n"/>
-      <c r="F35" s="15" t="n"/>
-      <c r="G35" s="15" t="n"/>
-      <c r="H35" s="16" t="n"/>
-      <c r="I35" s="16" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="n"/>
-      <c r="B36" s="16" t="n"/>
-      <c r="C36" s="16" t="n"/>
-      <c r="D36" s="15" t="n"/>
-      <c r="E36" s="15" t="n"/>
-      <c r="F36" s="15" t="n"/>
-      <c r="G36" s="15" t="n"/>
-      <c r="H36" s="16" t="n"/>
-      <c r="I36" s="16" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="15" t="n"/>
-      <c r="B37" s="16" t="n"/>
-      <c r="C37" s="16" t="n"/>
-      <c r="D37" s="15" t="n"/>
-      <c r="E37" s="15" t="n"/>
-      <c r="F37" s="15" t="n"/>
-      <c r="G37" s="15" t="n"/>
-      <c r="H37" s="16" t="n"/>
-      <c r="I37" s="16" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="15" t="n"/>
-      <c r="B38" s="16" t="n"/>
-      <c r="C38" s="16" t="n"/>
-      <c r="D38" s="15" t="n"/>
-      <c r="E38" s="15" t="n"/>
-      <c r="F38" s="15" t="n"/>
-      <c r="G38" s="15" t="n"/>
-      <c r="H38" s="16" t="n"/>
-      <c r="I38" s="16" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="15" t="n"/>
-      <c r="B39" s="16" t="n"/>
-      <c r="C39" s="16" t="n"/>
-      <c r="D39" s="15" t="n"/>
-      <c r="E39" s="15" t="n"/>
-      <c r="F39" s="15" t="n"/>
-      <c r="G39" s="15" t="n"/>
-      <c r="H39" s="16" t="n"/>
-      <c r="I39" s="16" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="15" t="n"/>
-      <c r="B40" s="16" t="n"/>
-      <c r="C40" s="16" t="n"/>
-      <c r="D40" s="15" t="n"/>
-      <c r="E40" s="15" t="n"/>
-      <c r="F40" s="15" t="n"/>
-      <c r="G40" s="15" t="n"/>
-      <c r="H40" s="16" t="n"/>
-      <c r="I40" s="16" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="15" t="n"/>
-      <c r="B41" s="16" t="n"/>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="15" t="n"/>
-      <c r="E41" s="15" t="n"/>
-      <c r="F41" s="15" t="n"/>
-      <c r="G41" s="15" t="n"/>
-      <c r="H41" s="16" t="n"/>
-      <c r="I41" s="16" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="15" t="n"/>
-      <c r="B42" s="16" t="n"/>
-      <c r="C42" s="16" t="n"/>
-      <c r="D42" s="15" t="n"/>
-      <c r="E42" s="15" t="n"/>
-      <c r="F42" s="15" t="n"/>
-      <c r="G42" s="15" t="n"/>
-      <c r="H42" s="16" t="n"/>
-      <c r="I42" s="16" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="15" t="n"/>
-      <c r="B43" s="16" t="n"/>
-      <c r="C43" s="16" t="n"/>
-      <c r="D43" s="15" t="n"/>
-      <c r="E43" s="15" t="n"/>
-      <c r="F43" s="15" t="n"/>
-      <c r="G43" s="15" t="n"/>
-      <c r="H43" s="16" t="n"/>
-      <c r="I43" s="16" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="15" t="n"/>
-      <c r="B44" s="16" t="n"/>
-      <c r="C44" s="16" t="n"/>
-      <c r="D44" s="15" t="n"/>
-      <c r="E44" s="15" t="n"/>
-      <c r="F44" s="15" t="n"/>
-      <c r="G44" s="15" t="n"/>
-      <c r="H44" s="16" t="n"/>
-      <c r="I44" s="16" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="15" t="n"/>
-      <c r="B45" s="16" t="n"/>
-      <c r="C45" s="16" t="n"/>
-      <c r="D45" s="15" t="n"/>
-      <c r="E45" s="15" t="n"/>
-      <c r="F45" s="15" t="n"/>
-      <c r="G45" s="15" t="n"/>
-      <c r="H45" s="16" t="n"/>
-      <c r="I45" s="16" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="15" t="n"/>
-      <c r="B46" s="16" t="n"/>
-      <c r="C46" s="16" t="n"/>
-      <c r="D46" s="15" t="n"/>
-      <c r="E46" s="15" t="n"/>
-      <c r="F46" s="15" t="n"/>
-      <c r="G46" s="15" t="n"/>
-      <c r="H46" s="16" t="n"/>
-      <c r="I46" s="16" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="15" t="n"/>
-      <c r="B47" s="16" t="n"/>
-      <c r="C47" s="16" t="n"/>
-      <c r="D47" s="15" t="n"/>
-      <c r="E47" s="15" t="n"/>
-      <c r="F47" s="15" t="n"/>
-      <c r="G47" s="15" t="n"/>
-      <c r="H47" s="16" t="n"/>
-      <c r="I47" s="16" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="15" t="n"/>
-      <c r="B48" s="16" t="n"/>
-      <c r="C48" s="16" t="n"/>
-      <c r="D48" s="15" t="n"/>
-      <c r="E48" s="15" t="n"/>
-      <c r="F48" s="15" t="n"/>
-      <c r="G48" s="15" t="n"/>
-      <c r="H48" s="16" t="n"/>
-      <c r="I48" s="16" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="15" t="n"/>
-      <c r="B49" s="16" t="n"/>
-      <c r="C49" s="16" t="n"/>
-      <c r="D49" s="15" t="n"/>
-      <c r="E49" s="15" t="n"/>
-      <c r="F49" s="15" t="n"/>
-      <c r="G49" s="15" t="n"/>
-      <c r="H49" s="16" t="n"/>
-      <c r="I49" s="16" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="15" t="n"/>
-      <c r="B50" s="16" t="n"/>
-      <c r="C50" s="16" t="n"/>
-      <c r="D50" s="15" t="n"/>
-      <c r="E50" s="15" t="n"/>
-      <c r="F50" s="15" t="n"/>
-      <c r="G50" s="15" t="n"/>
-      <c r="H50" s="16" t="n"/>
-      <c r="I50" s="16" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="15" t="n"/>
-      <c r="B51" s="16" t="n"/>
-      <c r="C51" s="16" t="n"/>
-      <c r="D51" s="15" t="n"/>
-      <c r="E51" s="15" t="n"/>
-      <c r="F51" s="15" t="n"/>
-      <c r="G51" s="15" t="n"/>
-      <c r="H51" s="16" t="n"/>
-      <c r="I51" s="16" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="15" t="n"/>
-      <c r="B52" s="16" t="n"/>
-      <c r="C52" s="16" t="n"/>
-      <c r="D52" s="15" t="n"/>
-      <c r="E52" s="15" t="n"/>
-      <c r="F52" s="15" t="n"/>
-      <c r="G52" s="15" t="n"/>
-      <c r="H52" s="16" t="n"/>
-      <c r="I52" s="16" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="15" t="n"/>
-      <c r="B53" s="16" t="n"/>
-      <c r="C53" s="16" t="n"/>
-      <c r="D53" s="15" t="n"/>
-      <c r="E53" s="15" t="n"/>
-      <c r="F53" s="15" t="n"/>
-      <c r="G53" s="15" t="n"/>
-      <c r="H53" s="16" t="n"/>
-      <c r="I53" s="16" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="15" t="n"/>
-      <c r="B54" s="16" t="n"/>
-      <c r="C54" s="16" t="n"/>
-      <c r="D54" s="15" t="n"/>
-      <c r="E54" s="15" t="n"/>
-      <c r="F54" s="15" t="n"/>
-      <c r="G54" s="15" t="n"/>
-      <c r="H54" s="16" t="n"/>
-      <c r="I54" s="16" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="15" t="n"/>
-      <c r="B55" s="16" t="n"/>
-      <c r="C55" s="16" t="n"/>
-      <c r="D55" s="15" t="n"/>
-      <c r="E55" s="15" t="n"/>
-      <c r="F55" s="15" t="n"/>
-      <c r="G55" s="15" t="n"/>
-      <c r="H55" s="16" t="n"/>
-      <c r="I55" s="16" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="15" t="n"/>
-      <c r="B56" s="16" t="n"/>
-      <c r="C56" s="16" t="n"/>
-      <c r="D56" s="15" t="n"/>
-      <c r="E56" s="15" t="n"/>
-      <c r="F56" s="15" t="n"/>
-      <c r="G56" s="15" t="n"/>
-      <c r="H56" s="16" t="n"/>
-      <c r="I56" s="16" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="15" t="n"/>
-      <c r="B57" s="16" t="n"/>
-      <c r="C57" s="16" t="n"/>
-      <c r="D57" s="15" t="n"/>
-      <c r="E57" s="15" t="n"/>
-      <c r="F57" s="15" t="n"/>
-      <c r="G57" s="15" t="n"/>
-      <c r="H57" s="16" t="n"/>
-      <c r="I57" s="16" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="15" t="n"/>
-      <c r="B58" s="16" t="n"/>
-      <c r="C58" s="16" t="n"/>
-      <c r="D58" s="15" t="n"/>
-      <c r="E58" s="15" t="n"/>
-      <c r="F58" s="15" t="n"/>
-      <c r="G58" s="15" t="n"/>
-      <c r="H58" s="16" t="n"/>
-      <c r="I58" s="16" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="15" t="n"/>
-      <c r="B59" s="16" t="n"/>
-      <c r="C59" s="16" t="n"/>
-      <c r="D59" s="15" t="n"/>
-      <c r="E59" s="15" t="n"/>
-      <c r="F59" s="15" t="n"/>
-      <c r="G59" s="15" t="n"/>
-      <c r="H59" s="16" t="n"/>
-      <c r="I59" s="16" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="15" t="n"/>
-      <c r="B60" s="16" t="n"/>
-      <c r="C60" s="16" t="n"/>
-      <c r="D60" s="15" t="n"/>
-      <c r="E60" s="15" t="n"/>
-      <c r="F60" s="15" t="n"/>
-      <c r="G60" s="15" t="n"/>
-      <c r="H60" s="16" t="n"/>
-      <c r="I60" s="16" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="15" t="n"/>
-      <c r="B61" s="16" t="n"/>
-      <c r="C61" s="16" t="n"/>
-      <c r="D61" s="15" t="n"/>
-      <c r="E61" s="15" t="n"/>
-      <c r="F61" s="15" t="n"/>
-      <c r="G61" s="15" t="n"/>
-      <c r="H61" s="16" t="n"/>
-      <c r="I61" s="16" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="15" t="n"/>
-      <c r="B62" s="16" t="n"/>
-      <c r="C62" s="16" t="n"/>
-      <c r="D62" s="15" t="n"/>
-      <c r="E62" s="15" t="n"/>
-      <c r="F62" s="15" t="n"/>
-      <c r="G62" s="15" t="n"/>
-      <c r="H62" s="16" t="n"/>
-      <c r="I62" s="16" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="15" t="n"/>
-      <c r="B63" s="16" t="n"/>
-      <c r="C63" s="16" t="n"/>
-      <c r="D63" s="15" t="n"/>
-      <c r="E63" s="15" t="n"/>
-      <c r="F63" s="15" t="n"/>
-      <c r="G63" s="15" t="n"/>
-      <c r="H63" s="16" t="n"/>
-      <c r="I63" s="16" t="n"/>
+      <c r="F63" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="G63" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H63" s="24" t="inlineStr">
+        <is>
+          <t>박현준</t>
+        </is>
+      </c>
+      <c r="I63" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="15" t="n"/>
-      <c r="B64" s="16" t="n"/>
-      <c r="C64" s="16" t="n"/>
-      <c r="D64" s="15" t="n"/>
-      <c r="E64" s="15" t="n"/>
-      <c r="F64" s="15" t="n"/>
-      <c r="G64" s="15" t="n"/>
-      <c r="H64" s="16" t="n"/>
-      <c r="I64" s="16" t="n"/>
+      <c r="A64" s="21" t="inlineStr">
+        <is>
+          <t>q036</t>
+        </is>
+      </c>
+      <c r="B64" s="22" t="inlineStr">
+        <is>
+          <t>SggDZVu0DPk</t>
+        </is>
+      </c>
+      <c r="C64" s="22" t="inlineStr">
+        <is>
+          <t>김치랑 고기의 양은 얼마나 넣어?</t>
+        </is>
+      </c>
+      <c r="D64" s="21" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E64" s="21" t="n"/>
+      <c r="F64" s="21" t="n"/>
+      <c r="G64" s="21" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H64" s="22" t="inlineStr">
+        <is>
+          <t>박현준</t>
+        </is>
+      </c>
+      <c r="I64" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="15" t="n"/>
-      <c r="B65" s="16" t="n"/>
-      <c r="C65" s="16" t="n"/>
-      <c r="D65" s="15" t="n"/>
-      <c r="E65" s="15" t="n"/>
-      <c r="F65" s="15" t="n"/>
-      <c r="G65" s="15" t="n"/>
-      <c r="H65" s="16" t="n"/>
-      <c r="I65" s="16" t="n"/>
+      <c r="A65" s="21" t="inlineStr">
+        <is>
+          <t>q037</t>
+        </is>
+      </c>
+      <c r="B65" s="22" t="inlineStr">
+        <is>
+          <t>sfPYotqyD18</t>
+        </is>
+      </c>
+      <c r="C65" s="22" t="inlineStr">
+        <is>
+          <t>물은 얼마나 넣어?</t>
+        </is>
+      </c>
+      <c r="D65" s="21" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E65" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="F65" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="G65" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H65" s="22" t="inlineStr">
+        <is>
+          <t>박현준</t>
+        </is>
+      </c>
+      <c r="I65" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="15" t="n"/>
-      <c r="B66" s="16" t="n"/>
-      <c r="C66" s="16" t="n"/>
-      <c r="D66" s="15" t="n"/>
-      <c r="E66" s="15" t="n"/>
-      <c r="F66" s="15" t="n"/>
-      <c r="G66" s="15" t="n"/>
-      <c r="H66" s="16" t="n"/>
-      <c r="I66" s="16" t="n"/>
+      <c r="A66" s="23" t="inlineStr">
+        <is>
+          <t>q037</t>
+        </is>
+      </c>
+      <c r="B66" s="24" t="inlineStr">
+        <is>
+          <t>sfPYotqyD18</t>
+        </is>
+      </c>
+      <c r="C66" s="24" t="inlineStr">
+        <is>
+          <t>물은 얼마나 넣어?</t>
+        </is>
+      </c>
+      <c r="D66" s="23" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E66" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F66" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="G66" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H66" s="24" t="inlineStr">
+        <is>
+          <t>박현준</t>
+        </is>
+      </c>
+      <c r="I66" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="15" t="n"/>
-      <c r="B67" s="16" t="n"/>
-      <c r="C67" s="16" t="n"/>
-      <c r="D67" s="15" t="n"/>
-      <c r="E67" s="15" t="n"/>
-      <c r="F67" s="15" t="n"/>
-      <c r="G67" s="15" t="n"/>
-      <c r="H67" s="16" t="n"/>
-      <c r="I67" s="16" t="n"/>
+      <c r="A67" s="21" t="inlineStr">
+        <is>
+          <t>q038</t>
+        </is>
+      </c>
+      <c r="B67" s="22" t="inlineStr">
+        <is>
+          <t>sfPYotqyD18</t>
+        </is>
+      </c>
+      <c r="C67" s="22" t="inlineStr">
+        <is>
+          <t>소스는 얼마나 넣어?</t>
+        </is>
+      </c>
+      <c r="D67" s="21" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E67" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="F67" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="G67" s="21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H67" s="22" t="inlineStr">
+        <is>
+          <t>박현준</t>
+        </is>
+      </c>
+      <c r="I67" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" s="15" t="n"/>
-      <c r="B68" s="16" t="n"/>
-      <c r="C68" s="16" t="n"/>
-      <c r="D68" s="15" t="n"/>
-      <c r="E68" s="15" t="n"/>
-      <c r="F68" s="15" t="n"/>
-      <c r="G68" s="15" t="n"/>
-      <c r="H68" s="16" t="n"/>
-      <c r="I68" s="16" t="n"/>
+      <c r="A68" s="21" t="inlineStr">
+        <is>
+          <t>q039</t>
+        </is>
+      </c>
+      <c r="B68" s="22" t="inlineStr">
+        <is>
+          <t>sfPYotqyD18</t>
+        </is>
+      </c>
+      <c r="C68" s="22" t="inlineStr">
+        <is>
+          <t>페퍼로니는 얼마나 넣어?</t>
+        </is>
+      </c>
+      <c r="D68" s="21" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E68" s="21" t="n"/>
+      <c r="F68" s="21" t="n"/>
+      <c r="G68" s="21" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H68" s="22" t="inlineStr">
+        <is>
+          <t>박현준</t>
+        </is>
+      </c>
+      <c r="I68" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="15" t="n"/>
-      <c r="B69" s="16" t="n"/>
-      <c r="C69" s="16" t="n"/>
-      <c r="D69" s="15" t="n"/>
-      <c r="E69" s="15" t="n"/>
-      <c r="F69" s="15" t="n"/>
-      <c r="G69" s="15" t="n"/>
-      <c r="H69" s="16" t="n"/>
-      <c r="I69" s="16" t="n"/>
+      <c r="A69" s="21" t="inlineStr">
+        <is>
+          <t>q040</t>
+        </is>
+      </c>
+      <c r="B69" s="22" t="inlineStr">
+        <is>
+          <t>Z7z0wW62obE</t>
+        </is>
+      </c>
+      <c r="C69" s="22" t="inlineStr">
+        <is>
+          <t>고기는 얼마나 사용해?</t>
+        </is>
+      </c>
+      <c r="D69" s="21" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E69" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="F69" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="G69" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H69" s="22" t="inlineStr">
+        <is>
+          <t>박현준</t>
+        </is>
+      </c>
+      <c r="I69" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="15" t="n"/>
-      <c r="B70" s="16" t="n"/>
-      <c r="C70" s="16" t="n"/>
-      <c r="D70" s="15" t="n"/>
-      <c r="E70" s="15" t="n"/>
-      <c r="F70" s="15" t="n"/>
-      <c r="G70" s="15" t="n"/>
-      <c r="H70" s="16" t="n"/>
-      <c r="I70" s="16" t="n"/>
+      <c r="A70" s="23" t="inlineStr">
+        <is>
+          <t>q040</t>
+        </is>
+      </c>
+      <c r="B70" s="24" t="inlineStr">
+        <is>
+          <t>Z7z0wW62obE</t>
+        </is>
+      </c>
+      <c r="C70" s="24" t="inlineStr">
+        <is>
+          <t>고기는 얼마나 사용해?</t>
+        </is>
+      </c>
+      <c r="D70" s="23" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E70" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="F70" s="23" t="n">
+        <v>15</v>
+      </c>
+      <c r="G70" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H70" s="24" t="inlineStr">
+        <is>
+          <t>박현준</t>
+        </is>
+      </c>
+      <c r="I70" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" s="15" t="n"/>
-      <c r="B71" s="16" t="n"/>
-      <c r="C71" s="16" t="n"/>
-      <c r="D71" s="15" t="n"/>
-      <c r="E71" s="15" t="n"/>
-      <c r="F71" s="15" t="n"/>
-      <c r="G71" s="15" t="n"/>
-      <c r="H71" s="16" t="n"/>
-      <c r="I71" s="16" t="n"/>
+      <c r="A71" s="21" t="inlineStr">
+        <is>
+          <t>q041</t>
+        </is>
+      </c>
+      <c r="B71" s="22" t="inlineStr">
+        <is>
+          <t>Z7z0wW62obE</t>
+        </is>
+      </c>
+      <c r="C71" s="22" t="inlineStr">
+        <is>
+          <t>고기에 전분은 얼마나 묻혀?</t>
+        </is>
+      </c>
+      <c r="D71" s="21" t="inlineStr">
+        <is>
+          <t>시각적상태</t>
+        </is>
+      </c>
+      <c r="E71" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="F71" s="21" t="n">
+        <v>23</v>
+      </c>
+      <c r="G71" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H71" s="22" t="inlineStr">
+        <is>
+          <t>박현준</t>
+        </is>
+      </c>
+      <c r="I71" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" s="15" t="n"/>
-      <c r="B72" s="16" t="n"/>
-      <c r="C72" s="16" t="n"/>
-      <c r="D72" s="15" t="n"/>
-      <c r="E72" s="15" t="n"/>
-      <c r="F72" s="15" t="n"/>
-      <c r="G72" s="15" t="n"/>
-      <c r="H72" s="16" t="n"/>
-      <c r="I72" s="16" t="n"/>
+      <c r="A72" s="23" t="inlineStr">
+        <is>
+          <t>q041</t>
+        </is>
+      </c>
+      <c r="B72" s="24" t="inlineStr">
+        <is>
+          <t>Z7z0wW62obE</t>
+        </is>
+      </c>
+      <c r="C72" s="24" t="inlineStr">
+        <is>
+          <t>고기에 전분은 얼마나 묻혀?</t>
+        </is>
+      </c>
+      <c r="D72" s="23" t="inlineStr">
+        <is>
+          <t>시각적상태</t>
+        </is>
+      </c>
+      <c r="E72" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="F72" s="23" t="n">
+        <v>20</v>
+      </c>
+      <c r="G72" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H72" s="24" t="inlineStr">
+        <is>
+          <t>박현준</t>
+        </is>
+      </c>
+      <c r="I72" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" s="15" t="n"/>
-      <c r="B73" s="16" t="n"/>
-      <c r="C73" s="16" t="n"/>
-      <c r="D73" s="15" t="n"/>
-      <c r="E73" s="15" t="n"/>
-      <c r="F73" s="15" t="n"/>
-      <c r="G73" s="15" t="n"/>
-      <c r="H73" s="16" t="n"/>
-      <c r="I73" s="16" t="n"/>
+      <c r="A73" s="21" t="inlineStr">
+        <is>
+          <t>q042</t>
+        </is>
+      </c>
+      <c r="B73" s="22" t="inlineStr">
+        <is>
+          <t>Z7z0wW62obE</t>
+        </is>
+      </c>
+      <c r="C73" s="22" t="inlineStr">
+        <is>
+          <t>고추장은 얼마나 사용해?</t>
+        </is>
+      </c>
+      <c r="D73" s="21" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E73" s="21" t="n"/>
+      <c r="F73" s="21" t="n"/>
+      <c r="G73" s="21" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H73" s="22" t="inlineStr">
+        <is>
+          <t>박현준</t>
+        </is>
+      </c>
+      <c r="I73" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" s="15" t="n"/>
-      <c r="B74" s="16" t="n"/>
-      <c r="C74" s="16" t="n"/>
-      <c r="D74" s="15" t="n"/>
-      <c r="E74" s="15" t="n"/>
-      <c r="F74" s="15" t="n"/>
-      <c r="G74" s="15" t="n"/>
-      <c r="H74" s="16" t="n"/>
-      <c r="I74" s="16" t="n"/>
+      <c r="A74" s="21" t="inlineStr">
+        <is>
+          <t>q043</t>
+        </is>
+      </c>
+      <c r="B74" s="22" t="inlineStr">
+        <is>
+          <t>Z7z0wW62obE</t>
+        </is>
+      </c>
+      <c r="C74" s="22" t="inlineStr">
+        <is>
+          <t>고기 몇 분동안 구워?</t>
+        </is>
+      </c>
+      <c r="D74" s="21" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E74" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="F74" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="G74" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H74" s="22" t="inlineStr">
+        <is>
+          <t>박현준</t>
+        </is>
+      </c>
+      <c r="I74" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" s="15" t="n"/>
-      <c r="B75" s="16" t="n"/>
-      <c r="C75" s="16" t="n"/>
-      <c r="D75" s="15" t="n"/>
-      <c r="E75" s="15" t="n"/>
-      <c r="F75" s="15" t="n"/>
-      <c r="G75" s="15" t="n"/>
-      <c r="H75" s="16" t="n"/>
-      <c r="I75" s="16" t="n"/>
+      <c r="A75" s="23" t="inlineStr">
+        <is>
+          <t>q043</t>
+        </is>
+      </c>
+      <c r="B75" s="24" t="inlineStr">
+        <is>
+          <t>Z7z0wW62obE</t>
+        </is>
+      </c>
+      <c r="C75" s="24" t="inlineStr">
+        <is>
+          <t>고기 몇 분동안 구워?</t>
+        </is>
+      </c>
+      <c r="D75" s="23" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E75" s="23" t="n">
+        <v>36</v>
+      </c>
+      <c r="F75" s="23" t="n">
+        <v>40</v>
+      </c>
+      <c r="G75" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H75" s="24" t="inlineStr">
+        <is>
+          <t>박현준</t>
+        </is>
+      </c>
+      <c r="I75" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" s="15" t="n"/>
-      <c r="B76" s="16" t="n"/>
-      <c r="C76" s="16" t="n"/>
-      <c r="D76" s="15" t="n"/>
-      <c r="E76" s="15" t="n"/>
-      <c r="F76" s="15" t="n"/>
-      <c r="G76" s="15" t="n"/>
-      <c r="H76" s="16" t="n"/>
-      <c r="I76" s="16" t="n"/>
+      <c r="A76" s="21" t="inlineStr">
+        <is>
+          <t>q044</t>
+        </is>
+      </c>
+      <c r="B76" s="22" t="inlineStr">
+        <is>
+          <t>Z7z0wW62obE</t>
+        </is>
+      </c>
+      <c r="C76" s="22" t="inlineStr">
+        <is>
+          <t>소스가 충분히 졸아든 장면 보여줘</t>
+        </is>
+      </c>
+      <c r="D76" s="21" t="inlineStr">
+        <is>
+          <t>시각적상태</t>
+        </is>
+      </c>
+      <c r="E76" s="21" t="n">
+        <v>48</v>
+      </c>
+      <c r="F76" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="G76" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H76" s="22" t="inlineStr">
+        <is>
+          <t>박현준</t>
+        </is>
+      </c>
+      <c r="I76" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" s="15" t="n"/>
-      <c r="B77" s="16" t="n"/>
-      <c r="C77" s="16" t="n"/>
-      <c r="D77" s="15" t="n"/>
-      <c r="E77" s="15" t="n"/>
-      <c r="F77" s="15" t="n"/>
-      <c r="G77" s="15" t="n"/>
-      <c r="H77" s="16" t="n"/>
-      <c r="I77" s="16" t="n"/>
+      <c r="A77" s="23" t="inlineStr">
+        <is>
+          <t>q044</t>
+        </is>
+      </c>
+      <c r="B77" s="24" t="inlineStr">
+        <is>
+          <t>Z7z0wW62obE</t>
+        </is>
+      </c>
+      <c r="C77" s="24" t="inlineStr">
+        <is>
+          <t>소스가 충분히 졸아든 장면 보여줘</t>
+        </is>
+      </c>
+      <c r="D77" s="23" t="inlineStr">
+        <is>
+          <t>시각적상태</t>
+        </is>
+      </c>
+      <c r="E77" s="23" t="n">
+        <v>44</v>
+      </c>
+      <c r="F77" s="23" t="n">
+        <v>48</v>
+      </c>
+      <c r="G77" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H77" s="24" t="inlineStr">
+        <is>
+          <t>박현준</t>
+        </is>
+      </c>
+      <c r="I77" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" s="15" t="n"/>
-      <c r="B78" s="16" t="n"/>
-      <c r="C78" s="16" t="n"/>
-      <c r="D78" s="15" t="n"/>
-      <c r="E78" s="15" t="n"/>
-      <c r="F78" s="15" t="n"/>
-      <c r="G78" s="15" t="n"/>
-      <c r="H78" s="16" t="n"/>
-      <c r="I78" s="16" t="n"/>
+      <c r="A78" s="21" t="inlineStr">
+        <is>
+          <t>q045</t>
+        </is>
+      </c>
+      <c r="B78" s="22" t="inlineStr">
+        <is>
+          <t>Rjfzpzj3bug</t>
+        </is>
+      </c>
+      <c r="C78" s="22" t="inlineStr">
+        <is>
+          <t>전자레인지 몇 분 사용해?</t>
+        </is>
+      </c>
+      <c r="D78" s="21" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E78" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F78" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="G78" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H78" s="22" t="inlineStr">
+        <is>
+          <t>박현준</t>
+        </is>
+      </c>
+      <c r="I78" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="15" t="n"/>
-      <c r="B79" s="16" t="n"/>
-      <c r="C79" s="16" t="n"/>
-      <c r="D79" s="15" t="n"/>
-      <c r="E79" s="15" t="n"/>
-      <c r="F79" s="15" t="n"/>
-      <c r="G79" s="15" t="n"/>
-      <c r="H79" s="16" t="n"/>
-      <c r="I79" s="16" t="n"/>
+      <c r="A79" s="23" t="inlineStr">
+        <is>
+          <t>q045</t>
+        </is>
+      </c>
+      <c r="B79" s="24" t="inlineStr">
+        <is>
+          <t>Rjfzpzj3bug</t>
+        </is>
+      </c>
+      <c r="C79" s="24" t="inlineStr">
+        <is>
+          <t>전자레인지 몇 분 사용해?</t>
+        </is>
+      </c>
+      <c r="D79" s="23" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E79" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="G79" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H79" s="24" t="inlineStr">
+        <is>
+          <t>박현준</t>
+        </is>
+      </c>
+      <c r="I79" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="15" t="n"/>
-      <c r="B80" s="16" t="n"/>
-      <c r="C80" s="16" t="n"/>
-      <c r="D80" s="15" t="n"/>
-      <c r="E80" s="15" t="n"/>
-      <c r="F80" s="15" t="n"/>
-      <c r="G80" s="15" t="n"/>
-      <c r="H80" s="16" t="n"/>
-      <c r="I80" s="16" t="n"/>
+      <c r="A80" s="21" t="inlineStr">
+        <is>
+          <t>q046</t>
+        </is>
+      </c>
+      <c r="B80" s="22" t="inlineStr">
+        <is>
+          <t>Rjfzpzj3bug</t>
+        </is>
+      </c>
+      <c r="C80" s="22" t="inlineStr">
+        <is>
+          <t>에어프라이어기에 얼마나 구워?</t>
+        </is>
+      </c>
+      <c r="D80" s="21" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E80" s="21" t="n"/>
+      <c r="F80" s="21" t="n"/>
+      <c r="G80" s="21" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H80" s="22" t="inlineStr">
+        <is>
+          <t>박현준</t>
+        </is>
+      </c>
+      <c r="I80" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="15" t="n"/>
-      <c r="B81" s="16" t="n"/>
-      <c r="C81" s="16" t="n"/>
-      <c r="D81" s="15" t="n"/>
-      <c r="E81" s="15" t="n"/>
-      <c r="F81" s="15" t="n"/>
-      <c r="G81" s="15" t="n"/>
-      <c r="H81" s="16" t="n"/>
-      <c r="I81" s="16" t="n"/>
+      <c r="A81" s="21" t="inlineStr">
+        <is>
+          <t>q047</t>
+        </is>
+      </c>
+      <c r="B81" s="22" t="inlineStr">
+        <is>
+          <t>Rjfzpzj3bug</t>
+        </is>
+      </c>
+      <c r="C81" s="22" t="inlineStr">
+        <is>
+          <t>소스 레시피 알려줘</t>
+        </is>
+      </c>
+      <c r="D81" s="21" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E81" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="F81" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="G81" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H81" s="22" t="inlineStr">
+        <is>
+          <t>박현준</t>
+        </is>
+      </c>
+      <c r="I81" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="15" t="n"/>
-      <c r="B82" s="16" t="n"/>
-      <c r="C82" s="16" t="n"/>
-      <c r="D82" s="15" t="n"/>
-      <c r="E82" s="15" t="n"/>
-      <c r="F82" s="15" t="n"/>
-      <c r="G82" s="15" t="n"/>
-      <c r="H82" s="16" t="n"/>
-      <c r="I82" s="16" t="n"/>
+      <c r="A82" s="23" t="inlineStr">
+        <is>
+          <t>q047</t>
+        </is>
+      </c>
+      <c r="B82" s="24" t="inlineStr">
+        <is>
+          <t>Rjfzpzj3bug</t>
+        </is>
+      </c>
+      <c r="C82" s="24" t="inlineStr">
+        <is>
+          <t>소스 레시피 알려줘</t>
+        </is>
+      </c>
+      <c r="D82" s="23" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E82" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="F82" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="G82" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H82" s="24" t="inlineStr">
+        <is>
+          <t>박현준</t>
+        </is>
+      </c>
+      <c r="I82" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="15" t="n"/>
-      <c r="B83" s="16" t="n"/>
-      <c r="C83" s="16" t="n"/>
-      <c r="D83" s="15" t="n"/>
-      <c r="E83" s="15" t="n"/>
-      <c r="F83" s="15" t="n"/>
-      <c r="G83" s="15" t="n"/>
-      <c r="H83" s="16" t="n"/>
-      <c r="I83" s="16" t="n"/>
+      <c r="A83" s="21" t="inlineStr">
+        <is>
+          <t>q048</t>
+        </is>
+      </c>
+      <c r="B83" s="22" t="inlineStr">
+        <is>
+          <t>Rjfzpzj3bug</t>
+        </is>
+      </c>
+      <c r="C83" s="22" t="inlineStr">
+        <is>
+          <t>재료 소개하는 부분 보여줘</t>
+        </is>
+      </c>
+      <c r="D83" s="21" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E83" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="F83" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G83" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H83" s="22" t="inlineStr">
+        <is>
+          <t>박현준</t>
+        </is>
+      </c>
+      <c r="I83" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" s="15" t="n"/>
-      <c r="B84" s="16" t="n"/>
-      <c r="C84" s="16" t="n"/>
-      <c r="D84" s="15" t="n"/>
-      <c r="E84" s="15" t="n"/>
-      <c r="F84" s="15" t="n"/>
-      <c r="G84" s="15" t="n"/>
-      <c r="H84" s="16" t="n"/>
-      <c r="I84" s="16" t="n"/>
+      <c r="A84" s="23" t="inlineStr">
+        <is>
+          <t>q048</t>
+        </is>
+      </c>
+      <c r="B84" s="24" t="inlineStr">
+        <is>
+          <t>Rjfzpzj3bug</t>
+        </is>
+      </c>
+      <c r="C84" s="24" t="inlineStr">
+        <is>
+          <t>재료 소개하는 부분 보여줘</t>
+        </is>
+      </c>
+      <c r="D84" s="23" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E84" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F84" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="G84" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H84" s="24" t="inlineStr">
+        <is>
+          <t>박현준</t>
+        </is>
+      </c>
+      <c r="I84" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" s="15" t="n"/>
-      <c r="B85" s="16" t="n"/>
-      <c r="C85" s="16" t="n"/>
-      <c r="D85" s="15" t="n"/>
-      <c r="E85" s="15" t="n"/>
-      <c r="F85" s="15" t="n"/>
-      <c r="G85" s="15" t="n"/>
-      <c r="H85" s="16" t="n"/>
-      <c r="I85" s="16" t="n"/>
+      <c r="A85" s="21" t="inlineStr">
+        <is>
+          <t>q049</t>
+        </is>
+      </c>
+      <c r="B85" s="22" t="inlineStr">
+        <is>
+          <t>4due-wU9NFk</t>
+        </is>
+      </c>
+      <c r="C85" s="22" t="inlineStr">
+        <is>
+          <t>대파를 언제 넣어?</t>
+        </is>
+      </c>
+      <c r="D85" s="21" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E85" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="F85" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="G85" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H85" s="22" t="inlineStr">
+        <is>
+          <t>이태연</t>
+        </is>
+      </c>
+      <c r="I85" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" s="15" t="n"/>
-      <c r="B86" s="16" t="n"/>
-      <c r="C86" s="16" t="n"/>
-      <c r="D86" s="15" t="n"/>
-      <c r="E86" s="15" t="n"/>
-      <c r="F86" s="15" t="n"/>
-      <c r="G86" s="15" t="n"/>
-      <c r="H86" s="16" t="n"/>
-      <c r="I86" s="16" t="n"/>
+      <c r="A86" s="23" t="inlineStr">
+        <is>
+          <t>q049</t>
+        </is>
+      </c>
+      <c r="B86" s="24" t="inlineStr">
+        <is>
+          <t>4due-wU9NFk</t>
+        </is>
+      </c>
+      <c r="C86" s="24" t="inlineStr">
+        <is>
+          <t>대파를 언제 넣어?</t>
+        </is>
+      </c>
+      <c r="D86" s="23" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E86" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="F86" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="G86" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H86" s="24" t="inlineStr">
+        <is>
+          <t>이태연</t>
+        </is>
+      </c>
+      <c r="I86" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="15" t="n"/>
-      <c r="B87" s="16" t="n"/>
-      <c r="C87" s="16" t="n"/>
-      <c r="D87" s="15" t="n"/>
-      <c r="E87" s="15" t="n"/>
-      <c r="F87" s="15" t="n"/>
-      <c r="G87" s="15" t="n"/>
-      <c r="H87" s="16" t="n"/>
-      <c r="I87" s="16" t="n"/>
+      <c r="A87" s="21" t="inlineStr">
+        <is>
+          <t>q050</t>
+        </is>
+      </c>
+      <c r="B87" s="22" t="inlineStr">
+        <is>
+          <t>4due-wU9NFk</t>
+        </is>
+      </c>
+      <c r="C87" s="22" t="inlineStr">
+        <is>
+          <t>물을 얼마나 넣어?</t>
+        </is>
+      </c>
+      <c r="D87" s="21" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E87" s="21" t="n">
+        <v>35</v>
+      </c>
+      <c r="F87" s="21" t="n">
+        <v>41</v>
+      </c>
+      <c r="G87" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H87" s="22" t="inlineStr">
+        <is>
+          <t>이태연</t>
+        </is>
+      </c>
+      <c r="I87" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" s="15" t="n"/>
-      <c r="B88" s="16" t="n"/>
-      <c r="C88" s="16" t="n"/>
-      <c r="D88" s="15" t="n"/>
-      <c r="E88" s="15" t="n"/>
-      <c r="F88" s="15" t="n"/>
-      <c r="G88" s="15" t="n"/>
-      <c r="H88" s="16" t="n"/>
-      <c r="I88" s="16" t="n"/>
+      <c r="A88" s="23" t="inlineStr">
+        <is>
+          <t>q050</t>
+        </is>
+      </c>
+      <c r="B88" s="24" t="inlineStr">
+        <is>
+          <t>4due-wU9NFk</t>
+        </is>
+      </c>
+      <c r="C88" s="24" t="inlineStr">
+        <is>
+          <t>물을 얼마나 넣어?</t>
+        </is>
+      </c>
+      <c r="D88" s="23" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E88" s="23" t="n">
+        <v>31</v>
+      </c>
+      <c r="F88" s="23" t="n">
+        <v>35</v>
+      </c>
+      <c r="G88" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H88" s="24" t="inlineStr">
+        <is>
+          <t>이태연</t>
+        </is>
+      </c>
+      <c r="I88" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" s="15" t="n"/>
-      <c r="B89" s="16" t="n"/>
-      <c r="C89" s="16" t="n"/>
-      <c r="D89" s="15" t="n"/>
-      <c r="E89" s="15" t="n"/>
-      <c r="F89" s="15" t="n"/>
-      <c r="G89" s="15" t="n"/>
-      <c r="H89" s="16" t="n"/>
-      <c r="I89" s="16" t="n"/>
+      <c r="A89" s="21" t="inlineStr">
+        <is>
+          <t>q051</t>
+        </is>
+      </c>
+      <c r="B89" s="22" t="inlineStr">
+        <is>
+          <t>4due-wU9NFk</t>
+        </is>
+      </c>
+      <c r="C89" s="22" t="inlineStr">
+        <is>
+          <t>삼겹살은 얼마나 구워?</t>
+        </is>
+      </c>
+      <c r="D89" s="21" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E89" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="F89" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="G89" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H89" s="22" t="inlineStr">
+        <is>
+          <t>이태연</t>
+        </is>
+      </c>
+      <c r="I89" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" s="15" t="n"/>
-      <c r="B90" s="16" t="n"/>
-      <c r="C90" s="16" t="n"/>
-      <c r="D90" s="15" t="n"/>
-      <c r="E90" s="15" t="n"/>
-      <c r="F90" s="15" t="n"/>
-      <c r="G90" s="15" t="n"/>
-      <c r="H90" s="16" t="n"/>
-      <c r="I90" s="16" t="n"/>
+      <c r="A90" s="23" t="inlineStr">
+        <is>
+          <t>q051</t>
+        </is>
+      </c>
+      <c r="B90" s="24" t="inlineStr">
+        <is>
+          <t>4due-wU9NFk</t>
+        </is>
+      </c>
+      <c r="C90" s="24" t="inlineStr">
+        <is>
+          <t>삼겹살은 얼마나 구워?</t>
+        </is>
+      </c>
+      <c r="D90" s="23" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E90" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="G90" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H90" s="24" t="inlineStr">
+        <is>
+          <t>이태연</t>
+        </is>
+      </c>
+      <c r="I90" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" s="15" t="n"/>
-      <c r="B91" s="16" t="n"/>
-      <c r="C91" s="16" t="n"/>
-      <c r="D91" s="15" t="n"/>
-      <c r="E91" s="15" t="n"/>
-      <c r="F91" s="15" t="n"/>
-      <c r="G91" s="15" t="n"/>
-      <c r="H91" s="16" t="n"/>
-      <c r="I91" s="16" t="n"/>
+      <c r="A91" s="21" t="inlineStr">
+        <is>
+          <t>q052</t>
+        </is>
+      </c>
+      <c r="B91" s="22" t="inlineStr">
+        <is>
+          <t>4due-wU9NFk</t>
+        </is>
+      </c>
+      <c r="C91" s="22" t="inlineStr">
+        <is>
+          <t>고추장 얼마나 넣어?</t>
+        </is>
+      </c>
+      <c r="D91" s="21" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E91" s="21" t="n"/>
+      <c r="F91" s="21" t="n"/>
+      <c r="G91" s="21" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H91" s="22" t="inlineStr">
+        <is>
+          <t>이태연</t>
+        </is>
+      </c>
+      <c r="I91" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" s="15" t="n"/>
-      <c r="B92" s="16" t="n"/>
-      <c r="C92" s="16" t="n"/>
-      <c r="D92" s="15" t="n"/>
-      <c r="E92" s="15" t="n"/>
-      <c r="F92" s="15" t="n"/>
-      <c r="G92" s="15" t="n"/>
-      <c r="H92" s="16" t="n"/>
-      <c r="I92" s="16" t="n"/>
+      <c r="A92" s="21" t="inlineStr">
+        <is>
+          <t>q053</t>
+        </is>
+      </c>
+      <c r="B92" s="22" t="inlineStr">
+        <is>
+          <t>c5dmr5AQat0</t>
+        </is>
+      </c>
+      <c r="C92" s="22" t="inlineStr">
+        <is>
+          <t>설탕은 얼마나 넣어?</t>
+        </is>
+      </c>
+      <c r="D92" s="21" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E92" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="F92" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="G92" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H92" s="22" t="inlineStr">
+        <is>
+          <t>이태연</t>
+        </is>
+      </c>
+      <c r="I92" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" s="15" t="n"/>
-      <c r="B93" s="16" t="n"/>
-      <c r="C93" s="16" t="n"/>
-      <c r="D93" s="15" t="n"/>
-      <c r="E93" s="15" t="n"/>
-      <c r="F93" s="15" t="n"/>
-      <c r="G93" s="15" t="n"/>
-      <c r="H93" s="16" t="n"/>
-      <c r="I93" s="16" t="n"/>
+      <c r="A93" s="23" t="inlineStr">
+        <is>
+          <t>q053</t>
+        </is>
+      </c>
+      <c r="B93" s="24" t="inlineStr">
+        <is>
+          <t>c5dmr5AQat0</t>
+        </is>
+      </c>
+      <c r="C93" s="24" t="inlineStr">
+        <is>
+          <t>설탕은 얼마나 넣어?</t>
+        </is>
+      </c>
+      <c r="D93" s="23" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E93" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="F93" s="23" t="n">
+        <v>14</v>
+      </c>
+      <c r="G93" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H93" s="24" t="inlineStr">
+        <is>
+          <t>이태연</t>
+        </is>
+      </c>
+      <c r="I93" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" s="15" t="n"/>
-      <c r="B94" s="16" t="n"/>
-      <c r="C94" s="16" t="n"/>
-      <c r="D94" s="15" t="n"/>
-      <c r="E94" s="15" t="n"/>
-      <c r="F94" s="15" t="n"/>
-      <c r="G94" s="15" t="n"/>
-      <c r="H94" s="16" t="n"/>
-      <c r="I94" s="16" t="n"/>
+      <c r="A94" s="21" t="inlineStr">
+        <is>
+          <t>q054</t>
+        </is>
+      </c>
+      <c r="B94" s="22" t="inlineStr">
+        <is>
+          <t>c5dmr5AQat0</t>
+        </is>
+      </c>
+      <c r="C94" s="22" t="inlineStr">
+        <is>
+          <t>채소는 언제부터 넣어?</t>
+        </is>
+      </c>
+      <c r="D94" s="21" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E94" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="F94" s="21" t="n">
+        <v>42</v>
+      </c>
+      <c r="G94" s="21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H94" s="22" t="inlineStr">
+        <is>
+          <t>이태연</t>
+        </is>
+      </c>
+      <c r="I94" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" s="15" t="n"/>
-      <c r="B95" s="16" t="n"/>
-      <c r="C95" s="16" t="n"/>
-      <c r="D95" s="15" t="n"/>
-      <c r="E95" s="15" t="n"/>
-      <c r="F95" s="15" t="n"/>
-      <c r="G95" s="15" t="n"/>
-      <c r="H95" s="16" t="n"/>
-      <c r="I95" s="16" t="n"/>
+      <c r="A95" s="21" t="inlineStr">
+        <is>
+          <t>q055</t>
+        </is>
+      </c>
+      <c r="B95" s="22" t="inlineStr">
+        <is>
+          <t>c5dmr5AQat0</t>
+        </is>
+      </c>
+      <c r="C95" s="22" t="inlineStr">
+        <is>
+          <t>후추는 언제 넣어?</t>
+        </is>
+      </c>
+      <c r="D95" s="21" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E95" s="21" t="n">
+        <v>47</v>
+      </c>
+      <c r="F95" s="21" t="n">
+        <v>48</v>
+      </c>
+      <c r="G95" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H95" s="22" t="inlineStr">
+        <is>
+          <t>이태연</t>
+        </is>
+      </c>
+      <c r="I95" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" s="15" t="n"/>
-      <c r="B96" s="16" t="n"/>
-      <c r="C96" s="16" t="n"/>
-      <c r="D96" s="15" t="n"/>
-      <c r="E96" s="15" t="n"/>
-      <c r="F96" s="15" t="n"/>
-      <c r="G96" s="15" t="n"/>
-      <c r="H96" s="16" t="n"/>
-      <c r="I96" s="16" t="n"/>
+      <c r="A96" s="23" t="inlineStr">
+        <is>
+          <t>q055</t>
+        </is>
+      </c>
+      <c r="B96" s="24" t="inlineStr">
+        <is>
+          <t>c5dmr5AQat0</t>
+        </is>
+      </c>
+      <c r="C96" s="24" t="inlineStr">
+        <is>
+          <t>후추는 언제 넣어?</t>
+        </is>
+      </c>
+      <c r="D96" s="23" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E96" s="23" t="n">
+        <v>43</v>
+      </c>
+      <c r="F96" s="23" t="n">
+        <v>47</v>
+      </c>
+      <c r="G96" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H96" s="24" t="inlineStr">
+        <is>
+          <t>이태연</t>
+        </is>
+      </c>
+      <c r="I96" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" s="15" t="n"/>
-      <c r="B97" s="16" t="n"/>
-      <c r="C97" s="16" t="n"/>
-      <c r="D97" s="15" t="n"/>
-      <c r="E97" s="15" t="n"/>
-      <c r="F97" s="15" t="n"/>
-      <c r="G97" s="15" t="n"/>
-      <c r="H97" s="16" t="n"/>
-      <c r="I97" s="16" t="n"/>
+      <c r="A97" s="21" t="inlineStr">
+        <is>
+          <t>q056</t>
+        </is>
+      </c>
+      <c r="B97" s="22" t="inlineStr">
+        <is>
+          <t>c5dmr5AQat0</t>
+        </is>
+      </c>
+      <c r="C97" s="22" t="inlineStr">
+        <is>
+          <t>닭은 얼마나 노릇노릇하게 익혀?</t>
+        </is>
+      </c>
+      <c r="D97" s="21" t="inlineStr">
+        <is>
+          <t>시각적상태</t>
+        </is>
+      </c>
+      <c r="E97" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="F97" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="G97" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H97" s="22" t="inlineStr">
+        <is>
+          <t>이태연</t>
+        </is>
+      </c>
+      <c r="I97" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" s="15" t="n"/>
-      <c r="B98" s="16" t="n"/>
-      <c r="C98" s="16" t="n"/>
-      <c r="D98" s="15" t="n"/>
-      <c r="E98" s="15" t="n"/>
-      <c r="F98" s="15" t="n"/>
-      <c r="G98" s="15" t="n"/>
-      <c r="H98" s="16" t="n"/>
-      <c r="I98" s="16" t="n"/>
+      <c r="A98" s="23" t="inlineStr">
+        <is>
+          <t>q056</t>
+        </is>
+      </c>
+      <c r="B98" s="24" t="inlineStr">
+        <is>
+          <t>c5dmr5AQat0</t>
+        </is>
+      </c>
+      <c r="C98" s="24" t="inlineStr">
+        <is>
+          <t>닭은 얼마나 노릇노릇하게 익혀?</t>
+        </is>
+      </c>
+      <c r="D98" s="23" t="inlineStr">
+        <is>
+          <t>시각적상태</t>
+        </is>
+      </c>
+      <c r="E98" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="F98" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="G98" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H98" s="24" t="inlineStr">
+        <is>
+          <t>이태연</t>
+        </is>
+      </c>
+      <c r="I98" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" s="15" t="n"/>
-      <c r="B99" s="16" t="n"/>
-      <c r="C99" s="16" t="n"/>
-      <c r="D99" s="15" t="n"/>
-      <c r="E99" s="15" t="n"/>
-      <c r="F99" s="15" t="n"/>
-      <c r="G99" s="15" t="n"/>
-      <c r="H99" s="16" t="n"/>
-      <c r="I99" s="16" t="n"/>
+      <c r="A99" s="21" t="inlineStr">
+        <is>
+          <t>q057</t>
+        </is>
+      </c>
+      <c r="B99" s="22" t="inlineStr">
+        <is>
+          <t>l3WthBEFzFw</t>
+        </is>
+      </c>
+      <c r="C99" s="22" t="inlineStr">
+        <is>
+          <t>감자는 얼마나 넣어?</t>
+        </is>
+      </c>
+      <c r="D99" s="21" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E99" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="F99" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="G99" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H99" s="22" t="inlineStr">
+        <is>
+          <t>이태연</t>
+        </is>
+      </c>
+      <c r="I99" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="15" t="n"/>
-      <c r="B100" s="16" t="n"/>
-      <c r="C100" s="16" t="n"/>
-      <c r="D100" s="15" t="n"/>
-      <c r="E100" s="15" t="n"/>
-      <c r="F100" s="15" t="n"/>
-      <c r="G100" s="15" t="n"/>
-      <c r="H100" s="16" t="n"/>
-      <c r="I100" s="16" t="n"/>
+      <c r="A100" s="23" t="inlineStr">
+        <is>
+          <t>q057</t>
+        </is>
+      </c>
+      <c r="B100" s="24" t="inlineStr">
+        <is>
+          <t>l3WthBEFzFw</t>
+        </is>
+      </c>
+      <c r="C100" s="24" t="inlineStr">
+        <is>
+          <t>감자는 얼마나 넣어?</t>
+        </is>
+      </c>
+      <c r="D100" s="23" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E100" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="G100" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H100" s="24" t="inlineStr">
+        <is>
+          <t>이태연</t>
+        </is>
+      </c>
+      <c r="I100" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" s="15" t="n"/>
-      <c r="B101" s="16" t="n"/>
-      <c r="C101" s="16" t="n"/>
-      <c r="D101" s="15" t="n"/>
-      <c r="E101" s="15" t="n"/>
-      <c r="F101" s="15" t="n"/>
-      <c r="G101" s="15" t="n"/>
-      <c r="H101" s="16" t="n"/>
-      <c r="I101" s="16" t="n"/>
+      <c r="A101" s="21" t="inlineStr">
+        <is>
+          <t>q058</t>
+        </is>
+      </c>
+      <c r="B101" s="22" t="inlineStr">
+        <is>
+          <t>l3WthBEFzFw</t>
+        </is>
+      </c>
+      <c r="C101" s="22" t="inlineStr">
+        <is>
+          <t>전분은 언제 빼?</t>
+        </is>
+      </c>
+      <c r="D101" s="21" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E101" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="F101" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="G101" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H101" s="22" t="inlineStr">
+        <is>
+          <t>이태연</t>
+        </is>
+      </c>
+      <c r="I101" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" s="15" t="n"/>
-      <c r="B102" s="16" t="n"/>
-      <c r="C102" s="16" t="n"/>
-      <c r="D102" s="15" t="n"/>
-      <c r="E102" s="15" t="n"/>
-      <c r="F102" s="15" t="n"/>
-      <c r="G102" s="15" t="n"/>
-      <c r="H102" s="16" t="n"/>
-      <c r="I102" s="16" t="n"/>
+      <c r="A102" s="23" t="inlineStr">
+        <is>
+          <t>q058</t>
+        </is>
+      </c>
+      <c r="B102" s="24" t="inlineStr">
+        <is>
+          <t>l3WthBEFzFw</t>
+        </is>
+      </c>
+      <c r="C102" s="24" t="inlineStr">
+        <is>
+          <t>전분은 언제 빼?</t>
+        </is>
+      </c>
+      <c r="D102" s="23" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E102" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="F102" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="G102" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H102" s="24" t="inlineStr">
+        <is>
+          <t>이태연</t>
+        </is>
+      </c>
+      <c r="I102" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" s="15" t="n"/>
-      <c r="B103" s="16" t="n"/>
-      <c r="C103" s="16" t="n"/>
-      <c r="D103" s="15" t="n"/>
-      <c r="E103" s="15" t="n"/>
-      <c r="F103" s="15" t="n"/>
-      <c r="G103" s="15" t="n"/>
-      <c r="H103" s="16" t="n"/>
-      <c r="I103" s="16" t="n"/>
+      <c r="A103" s="21" t="inlineStr">
+        <is>
+          <t>q059</t>
+        </is>
+      </c>
+      <c r="B103" s="22" t="inlineStr">
+        <is>
+          <t>l3WthBEFzFw</t>
+        </is>
+      </c>
+      <c r="C103" s="22" t="inlineStr">
+        <is>
+          <t>감자는 얼마나 볶아?</t>
+        </is>
+      </c>
+      <c r="D103" s="21" t="inlineStr">
+        <is>
+          <t>시각적상태</t>
+        </is>
+      </c>
+      <c r="E103" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="F103" s="21" t="n">
+        <v>33</v>
+      </c>
+      <c r="G103" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H103" s="22" t="inlineStr">
+        <is>
+          <t>이태연</t>
+        </is>
+      </c>
+      <c r="I103" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" s="15" t="n"/>
-      <c r="B104" s="16" t="n"/>
-      <c r="C104" s="16" t="n"/>
-      <c r="D104" s="15" t="n"/>
-      <c r="E104" s="15" t="n"/>
-      <c r="F104" s="15" t="n"/>
-      <c r="G104" s="15" t="n"/>
-      <c r="H104" s="16" t="n"/>
-      <c r="I104" s="16" t="n"/>
+      <c r="A104" s="23" t="inlineStr">
+        <is>
+          <t>q059</t>
+        </is>
+      </c>
+      <c r="B104" s="24" t="inlineStr">
+        <is>
+          <t>l3WthBEFzFw</t>
+        </is>
+      </c>
+      <c r="C104" s="24" t="inlineStr">
+        <is>
+          <t>감자는 얼마나 볶아?</t>
+        </is>
+      </c>
+      <c r="D104" s="23" t="inlineStr">
+        <is>
+          <t>시각적상태</t>
+        </is>
+      </c>
+      <c r="E104" s="23" t="n">
+        <v>26</v>
+      </c>
+      <c r="F104" s="23" t="n">
+        <v>30</v>
+      </c>
+      <c r="G104" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H104" s="24" t="inlineStr">
+        <is>
+          <t>이태연</t>
+        </is>
+      </c>
+      <c r="I104" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
     </row>
     <row r="105">
-      <c r="A105" s="15" t="n"/>
-      <c r="B105" s="16" t="n"/>
-      <c r="C105" s="16" t="n"/>
-      <c r="D105" s="15" t="n"/>
-      <c r="E105" s="15" t="n"/>
-      <c r="F105" s="15" t="n"/>
-      <c r="G105" s="15" t="n"/>
-      <c r="H105" s="16" t="n"/>
-      <c r="I105" s="16" t="n"/>
+      <c r="A105" s="21" t="inlineStr">
+        <is>
+          <t>q060</t>
+        </is>
+      </c>
+      <c r="B105" s="22" t="inlineStr">
+        <is>
+          <t>l3WthBEFzFw</t>
+        </is>
+      </c>
+      <c r="C105" s="22" t="inlineStr">
+        <is>
+          <t>간장은 얼마나 넣어?</t>
+        </is>
+      </c>
+      <c r="D105" s="21" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E105" s="21" t="n">
+        <v>39</v>
+      </c>
+      <c r="F105" s="21" t="n">
+        <v>41</v>
+      </c>
+      <c r="G105" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H105" s="22" t="inlineStr">
+        <is>
+          <t>이태연</t>
+        </is>
+      </c>
+      <c r="I105" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" s="15" t="n"/>
-      <c r="B106" s="16" t="n"/>
-      <c r="C106" s="16" t="n"/>
-      <c r="D106" s="15" t="n"/>
-      <c r="E106" s="15" t="n"/>
-      <c r="F106" s="15" t="n"/>
-      <c r="G106" s="15" t="n"/>
-      <c r="H106" s="16" t="n"/>
-      <c r="I106" s="16" t="n"/>
+      <c r="A106" s="23" t="inlineStr">
+        <is>
+          <t>q060</t>
+        </is>
+      </c>
+      <c r="B106" s="24" t="inlineStr">
+        <is>
+          <t>l3WthBEFzFw</t>
+        </is>
+      </c>
+      <c r="C106" s="24" t="inlineStr">
+        <is>
+          <t>간장은 얼마나 넣어?</t>
+        </is>
+      </c>
+      <c r="D106" s="23" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E106" s="23" t="n">
+        <v>35</v>
+      </c>
+      <c r="F106" s="23" t="n">
+        <v>39</v>
+      </c>
+      <c r="G106" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H106" s="24" t="inlineStr">
+        <is>
+          <t>이태연</t>
+        </is>
+      </c>
+      <c r="I106" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
     </row>
     <row r="107">
-      <c r="A107" s="15" t="n"/>
-      <c r="B107" s="16" t="n"/>
-      <c r="C107" s="16" t="n"/>
-      <c r="D107" s="15" t="n"/>
-      <c r="E107" s="15" t="n"/>
-      <c r="F107" s="15" t="n"/>
-      <c r="G107" s="15" t="n"/>
-      <c r="H107" s="16" t="n"/>
-      <c r="I107" s="16" t="n"/>
+      <c r="A107" s="21" t="inlineStr">
+        <is>
+          <t>q061</t>
+        </is>
+      </c>
+      <c r="B107" s="22" t="inlineStr">
+        <is>
+          <t>OgR00HBMKFs</t>
+        </is>
+      </c>
+      <c r="C107" s="22" t="inlineStr">
+        <is>
+          <t>항정살은 어느 정도까지 익혀?</t>
+        </is>
+      </c>
+      <c r="D107" s="21" t="inlineStr">
+        <is>
+          <t>시각적상태</t>
+        </is>
+      </c>
+      <c r="E107" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="F107" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="G107" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H107" s="22" t="inlineStr">
+        <is>
+          <t>이태연</t>
+        </is>
+      </c>
+      <c r="I107" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" s="15" t="n"/>
-      <c r="B108" s="16" t="n"/>
-      <c r="C108" s="16" t="n"/>
-      <c r="D108" s="15" t="n"/>
-      <c r="E108" s="15" t="n"/>
-      <c r="F108" s="15" t="n"/>
-      <c r="G108" s="15" t="n"/>
-      <c r="H108" s="16" t="n"/>
-      <c r="I108" s="16" t="n"/>
+      <c r="A108" s="23" t="inlineStr">
+        <is>
+          <t>q061</t>
+        </is>
+      </c>
+      <c r="B108" s="24" t="inlineStr">
+        <is>
+          <t>OgR00HBMKFs</t>
+        </is>
+      </c>
+      <c r="C108" s="24" t="inlineStr">
+        <is>
+          <t>항정살은 어느 정도까지 익혀?</t>
+        </is>
+      </c>
+      <c r="D108" s="23" t="inlineStr">
+        <is>
+          <t>시각적상태</t>
+        </is>
+      </c>
+      <c r="E108" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="F108" s="23" t="n">
+        <v>14</v>
+      </c>
+      <c r="G108" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H108" s="24" t="inlineStr">
+        <is>
+          <t>이태연</t>
+        </is>
+      </c>
+      <c r="I108" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
     </row>
     <row r="109">
-      <c r="A109" s="15" t="n"/>
-      <c r="B109" s="16" t="n"/>
-      <c r="C109" s="16" t="n"/>
-      <c r="D109" s="15" t="n"/>
-      <c r="E109" s="15" t="n"/>
-      <c r="F109" s="15" t="n"/>
-      <c r="G109" s="15" t="n"/>
-      <c r="H109" s="16" t="n"/>
-      <c r="I109" s="16" t="n"/>
+      <c r="A109" s="21" t="inlineStr">
+        <is>
+          <t>q062</t>
+        </is>
+      </c>
+      <c r="B109" s="22" t="inlineStr">
+        <is>
+          <t>OgR00HBMKFs</t>
+        </is>
+      </c>
+      <c r="C109" s="22" t="inlineStr">
+        <is>
+          <t>두부는 언제 조리해?</t>
+        </is>
+      </c>
+      <c r="D109" s="21" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E109" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="F109" s="21" t="n">
+        <v>33</v>
+      </c>
+      <c r="G109" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H109" s="22" t="inlineStr">
+        <is>
+          <t>이태연</t>
+        </is>
+      </c>
+      <c r="I109" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
     </row>
     <row r="110">
-      <c r="A110" s="15" t="n"/>
-      <c r="B110" s="16" t="n"/>
-      <c r="C110" s="16" t="n"/>
-      <c r="D110" s="15" t="n"/>
-      <c r="E110" s="15" t="n"/>
-      <c r="F110" s="15" t="n"/>
-      <c r="G110" s="15" t="n"/>
-      <c r="H110" s="16" t="n"/>
-      <c r="I110" s="16" t="n"/>
+      <c r="A110" s="23" t="inlineStr">
+        <is>
+          <t>q062</t>
+        </is>
+      </c>
+      <c r="B110" s="24" t="inlineStr">
+        <is>
+          <t>OgR00HBMKFs</t>
+        </is>
+      </c>
+      <c r="C110" s="24" t="inlineStr">
+        <is>
+          <t>두부는 언제 조리해?</t>
+        </is>
+      </c>
+      <c r="D110" s="23" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E110" s="23" t="n">
+        <v>18</v>
+      </c>
+      <c r="F110" s="23" t="n">
+        <v>22</v>
+      </c>
+      <c r="G110" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H110" s="24" t="inlineStr">
+        <is>
+          <t>이태연</t>
+        </is>
+      </c>
+      <c r="I110" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
     </row>
     <row r="111">
-      <c r="A111" s="15" t="n"/>
-      <c r="B111" s="16" t="n"/>
-      <c r="C111" s="16" t="n"/>
-      <c r="D111" s="15" t="n"/>
-      <c r="E111" s="15" t="n"/>
-      <c r="F111" s="15" t="n"/>
-      <c r="G111" s="15" t="n"/>
-      <c r="H111" s="16" t="n"/>
-      <c r="I111" s="16" t="n"/>
+      <c r="A111" s="21" t="inlineStr">
+        <is>
+          <t>q063</t>
+        </is>
+      </c>
+      <c r="B111" s="22" t="inlineStr">
+        <is>
+          <t>OgR00HBMKFs</t>
+        </is>
+      </c>
+      <c r="C111" s="22" t="inlineStr">
+        <is>
+          <t>김치는 얼마나 넣어?</t>
+        </is>
+      </c>
+      <c r="D111" s="21" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E111" s="21" t="n">
+        <v>33</v>
+      </c>
+      <c r="F111" s="21" t="n">
+        <v>36</v>
+      </c>
+      <c r="G111" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H111" s="22" t="inlineStr">
+        <is>
+          <t>이태연</t>
+        </is>
+      </c>
+      <c r="I111" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
     </row>
     <row r="112">
-      <c r="A112" s="15" t="n"/>
-      <c r="B112" s="16" t="n"/>
-      <c r="C112" s="16" t="n"/>
-      <c r="D112" s="15" t="n"/>
-      <c r="E112" s="15" t="n"/>
-      <c r="F112" s="15" t="n"/>
-      <c r="G112" s="15" t="n"/>
-      <c r="H112" s="16" t="n"/>
-      <c r="I112" s="16" t="n"/>
+      <c r="A112" s="23" t="inlineStr">
+        <is>
+          <t>q063</t>
+        </is>
+      </c>
+      <c r="B112" s="24" t="inlineStr">
+        <is>
+          <t>OgR00HBMKFs</t>
+        </is>
+      </c>
+      <c r="C112" s="24" t="inlineStr">
+        <is>
+          <t>김치는 얼마나 넣어?</t>
+        </is>
+      </c>
+      <c r="D112" s="23" t="inlineStr">
+        <is>
+          <t>재료분량</t>
+        </is>
+      </c>
+      <c r="E112" s="23" t="n">
+        <v>29</v>
+      </c>
+      <c r="F112" s="23" t="n">
+        <v>33</v>
+      </c>
+      <c r="G112" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H112" s="24" t="inlineStr">
+        <is>
+          <t>이태연</t>
+        </is>
+      </c>
+      <c r="I112" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
     </row>
     <row r="113">
-      <c r="A113" s="15" t="n"/>
-      <c r="B113" s="16" t="n"/>
-      <c r="C113" s="16" t="n"/>
-      <c r="D113" s="15" t="n"/>
-      <c r="E113" s="15" t="n"/>
-      <c r="F113" s="15" t="n"/>
-      <c r="G113" s="15" t="n"/>
-      <c r="H113" s="16" t="n"/>
-      <c r="I113" s="16" t="n"/>
+      <c r="A113" s="21" t="inlineStr">
+        <is>
+          <t>q064</t>
+        </is>
+      </c>
+      <c r="B113" s="22" t="inlineStr">
+        <is>
+          <t>OgR00HBMKFs</t>
+        </is>
+      </c>
+      <c r="C113" s="22" t="inlineStr">
+        <is>
+          <t>대파와 청양고추는 언제 넣어?</t>
+        </is>
+      </c>
+      <c r="D113" s="21" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E113" s="21" t="n">
+        <v>72</v>
+      </c>
+      <c r="F113" s="21" t="n">
+        <v>67</v>
+      </c>
+      <c r="G113" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H113" s="22" t="inlineStr">
+        <is>
+          <t>이태연</t>
+        </is>
+      </c>
+      <c r="I113" s="22" t="inlineStr">
+        <is>
+          <t>원본</t>
+        </is>
+      </c>
     </row>
     <row r="114">
-      <c r="A114" s="15" t="n"/>
-      <c r="B114" s="16" t="n"/>
-      <c r="C114" s="16" t="n"/>
-      <c r="D114" s="15" t="n"/>
-      <c r="E114" s="15" t="n"/>
-      <c r="F114" s="15" t="n"/>
-      <c r="G114" s="15" t="n"/>
-      <c r="H114" s="16" t="n"/>
-      <c r="I114" s="16" t="n"/>
+      <c r="A114" s="23" t="inlineStr">
+        <is>
+          <t>q064</t>
+        </is>
+      </c>
+      <c r="B114" s="24" t="inlineStr">
+        <is>
+          <t>OgR00HBMKFs</t>
+        </is>
+      </c>
+      <c r="C114" s="24" t="inlineStr">
+        <is>
+          <t>대파와 청양고추는 언제 넣어?</t>
+        </is>
+      </c>
+      <c r="D114" s="23" t="inlineStr">
+        <is>
+          <t>순서타이밍</t>
+        </is>
+      </c>
+      <c r="E114" s="23" t="n">
+        <v>68</v>
+      </c>
+      <c r="F114" s="23" t="n">
+        <v>72</v>
+      </c>
+      <c r="G114" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H114" s="24" t="inlineStr">
+        <is>
+          <t>이태연</t>
+        </is>
+      </c>
+      <c r="I114" s="24" t="inlineStr">
+        <is>
+          <t>규칙생성</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="15" t="n"/>
@@ -5687,17 +9242,6 @@
       <c r="G398" s="15" t="n"/>
       <c r="H398" s="16" t="n"/>
       <c r="I398" s="16" t="n"/>
-    </row>
-    <row r="399">
-      <c r="A399" s="15" t="n"/>
-      <c r="B399" s="16" t="n"/>
-      <c r="C399" s="16" t="n"/>
-      <c r="D399" s="15" t="n"/>
-      <c r="E399" s="15" t="n"/>
-      <c r="F399" s="15" t="n"/>
-      <c r="G399" s="15" t="n"/>
-      <c r="H399" s="16" t="n"/>
-      <c r="I399" s="16" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -5721,7 +9265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6062,12 +9606,12 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>5AP-rJGheKk</t>
+          <t>jPqpNbPT7yY</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>요리 레시피 쇼츠</t>
+          <t>명절 전부치기 동태전 혼자서도 쉽게 쉽게 노릇하고 바삭하게 #집밥 #제철음식 #cooking #레시피 #반찬 #food #shourt #쇼츠</t>
         </is>
       </c>
       <c r="D11" s="16" t="inlineStr">
@@ -6076,11 +9620,11 @@
         </is>
       </c>
       <c r="E11" s="15" t="n">
-        <v>45.6</v>
+        <v>33.5</v>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5AP-rJGheKk</t>
+          <t>https://www.youtube.com/watch?v=jPqpNbPT7yY</t>
         </is>
       </c>
       <c r="G11" s="15" t="inlineStr">
@@ -6100,12 +9644,12 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>jPqpNbPT7yY</t>
+          <t>282ScDPvm28</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>명절 전부치기 동태전 혼자서도 쉽게 쉽게 노릇하고 바삭하게 #집밥 #제철음식 #cooking #레시피 #반찬 #food #shourt #쇼츠</t>
+          <t>짜장! 재료도 간단! 만들기도 간단! #shorts</t>
         </is>
       </c>
       <c r="D12" s="16" t="inlineStr">
@@ -6114,11 +9658,11 @@
         </is>
       </c>
       <c r="E12" s="15" t="n">
-        <v>33.5</v>
+        <v>30.9</v>
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=jPqpNbPT7yY</t>
+          <t>https://www.youtube.com/watch?v=282ScDPvm28</t>
         </is>
       </c>
       <c r="G12" s="15" t="inlineStr">
@@ -6138,12 +9682,12 @@
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>282ScDPvm28</t>
+          <t>sPeEcFdaD0M</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>짜장! 재료도 간단! 만들기도 간단! #shorts</t>
+          <t>너무 쉬워서 매일 먹는 두부 계란요리 Easy Tofu Egg Recipe</t>
         </is>
       </c>
       <c r="D13" s="16" t="inlineStr">
@@ -6152,11 +9696,11 @@
         </is>
       </c>
       <c r="E13" s="15" t="n">
-        <v>30.9</v>
+        <v>60</v>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=282ScDPvm28</t>
+          <t>https://www.youtube.com/watch?v=sPeEcFdaD0M</t>
         </is>
       </c>
       <c r="G13" s="15" t="inlineStr">
@@ -6176,12 +9720,12 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>sPeEcFdaD0M</t>
+          <t>rfkc9X4BItc</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>너무 쉬워서 매일 먹는 두부 계란요리 Easy Tofu Egg Recipe</t>
+          <t>입맛 없을 때 무조건 해보세요! 오징어 초무침 황금 레시피 #간단요리 #반찬만들기 #오징어</t>
         </is>
       </c>
       <c r="D14" s="16" t="inlineStr">
@@ -6190,11 +9734,11 @@
         </is>
       </c>
       <c r="E14" s="15" t="n">
-        <v>60</v>
+        <v>61.5</v>
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=sPeEcFdaD0M</t>
+          <t>https://www.youtube.com/watch?v=rfkc9X4BItc</t>
         </is>
       </c>
       <c r="G14" s="15" t="inlineStr">
@@ -6214,12 +9758,12 @@
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>rfkc9X4BItc</t>
+          <t>Hwzl8IA9NH0</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>입맛 없을 때 무조건 해보세요! 오징어 초무침 황금 레시피 #간단요리 #반찬만들기 #오징어</t>
+          <t>말도 안 되는 맛</t>
         </is>
       </c>
       <c r="D15" s="16" t="inlineStr">
@@ -6228,11 +9772,11 @@
         </is>
       </c>
       <c r="E15" s="15" t="n">
-        <v>61.5</v>
+        <v>27.9</v>
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rfkc9X4BItc</t>
+          <t>https://www.youtube.com/watch?v=Hwzl8IA9NH0</t>
         </is>
       </c>
       <c r="G15" s="15" t="inlineStr">
@@ -6252,12 +9796,12 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>Hwzl8IA9NH0</t>
+          <t>11C8XqWobjQ</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>말도 안 되는 맛</t>
+          <t>[⭐️490만⭐️] 초간단 4분 잔치국수 뚝딱! #shorts</t>
         </is>
       </c>
       <c r="D16" s="16" t="inlineStr">
@@ -6266,11 +9810,11 @@
         </is>
       </c>
       <c r="E16" s="15" t="n">
-        <v>27.9</v>
+        <v>40.5</v>
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Hwzl8IA9NH0</t>
+          <t>https://www.youtube.com/watch?v=11C8XqWobjQ</t>
         </is>
       </c>
       <c r="G16" s="15" t="inlineStr">
@@ -6290,12 +9834,12 @@
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>11C8XqWobjQ</t>
+          <t>iDMyw61V1XM</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>[⭐️490만⭐️] 초간단 4분 잔치국수 뚝딱! #shorts</t>
+          <t>지코바는 사 먹지 마세요!</t>
         </is>
       </c>
       <c r="D17" s="16" t="inlineStr">
@@ -6304,11 +9848,11 @@
         </is>
       </c>
       <c r="E17" s="15" t="n">
-        <v>40.5</v>
+        <v>55</v>
       </c>
       <c r="F17" s="17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=11C8XqWobjQ</t>
+          <t>https://www.youtube.com/watch?v=iDMyw61V1XM</t>
         </is>
       </c>
       <c r="G17" s="15" t="inlineStr">
@@ -6328,67 +9872,151 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>iDMyw61V1XM</t>
+          <t>l3WthBEFzFw</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>지코바는 사 먹지 마세요!</t>
+          <t>감자조림 한번보면 평생 써먹는 레시피 #shorts</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>후딱 레시피 Huttak</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E18" s="15" t="n">
+        <v>61</v>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=l3WthBEFzFw</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>4due-wU9NFk</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>삼겹살에 된장 넣었더니…🔥 밥도둑이 됐어요!</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="n">
         <v>55</v>
       </c>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=iDMyw61V1XM</t>
-        </is>
-      </c>
-      <c r="G18" s="15" t="inlineStr">
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=4due-wU9NFk</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
       </c>
-      <c r="H18" s="15" t="inlineStr">
+      <c r="H19" s="15" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="15" t="n"/>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="16" t="n"/>
-      <c r="D19" s="16" t="n"/>
-      <c r="E19" s="15" t="n"/>
-      <c r="F19" s="16" t="n"/>
-      <c r="G19" s="15" t="n"/>
-      <c r="H19" s="15" t="n"/>
-    </row>
     <row r="20">
-      <c r="A20" s="15" t="n"/>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="15" t="n"/>
-      <c r="F20" s="16" t="n"/>
-      <c r="G20" s="15" t="n"/>
-      <c r="H20" s="15" t="n"/>
+      <c r="A20" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>OgR00HBMKFs</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>와이프 친구들이 먹고 제발 팔아달라는 김치찜!</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>@1mincook</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>90</v>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=OgR00HBMKFs</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="n"/>
-      <c r="B21" s="16" t="n"/>
-      <c r="C21" s="16" t="n"/>
-      <c r="D21" s="16" t="n"/>
-      <c r="E21" s="15" t="n"/>
-      <c r="F21" s="16" t="n"/>
-      <c r="G21" s="15" t="n"/>
-      <c r="H21" s="15" t="n"/>
+      <c r="A21" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>c5dmr5AQat0</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>오백만 원짜리 마약찜닭 레시피 쇼츠 버전입니다. #Shorts</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>@1mincook</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=c5dmr5AQat0</t>
+        </is>
+      </c>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="n"/>
@@ -6660,15 +10288,45 @@
       <c r="G48" s="15" t="n"/>
       <c r="H48" s="15" t="n"/>
     </row>
-    <row r="50" ht="26" customHeight="1">
-      <c r="A50" s="18" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="15" t="n"/>
+      <c r="B49" s="16" t="n"/>
+      <c r="C49" s="16" t="n"/>
+      <c r="D49" s="16" t="n"/>
+      <c r="E49" s="15" t="n"/>
+      <c r="F49" s="16" t="n"/>
+      <c r="G49" s="15" t="n"/>
+      <c r="H49" s="15" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="15" t="n"/>
+      <c r="B50" s="16" t="n"/>
+      <c r="C50" s="16" t="n"/>
+      <c r="D50" s="16" t="n"/>
+      <c r="E50" s="15" t="n"/>
+      <c r="F50" s="16" t="n"/>
+      <c r="G50" s="15" t="n"/>
+      <c r="H50" s="15" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="15" t="n"/>
+      <c r="B51" s="16" t="n"/>
+      <c r="C51" s="16" t="n"/>
+      <c r="D51" s="16" t="n"/>
+      <c r="E51" s="15" t="n"/>
+      <c r="F51" s="16" t="n"/>
+      <c r="G51" s="15" t="n"/>
+      <c r="H51" s="15" t="n"/>
+    </row>
+    <row r="53" ht="26" customHeight="1">
+      <c r="A53" s="18" t="inlineStr">
         <is>
           <t>· '질문 대상' 칸에 O 를 적은 영상에만 질문을 만듭니다. 저장 영상 25개 중 12~15개만 O 로 두고, 나머지는 검색 난이도를 유지하는 오답 후보로 남겨둡니다.</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="26" customHeight="1">
-      <c r="A51" s="18" t="inlineStr">
+    <row r="54" ht="26" customHeight="1">
+      <c r="A54" s="18" t="inlineStr">
         <is>
           <t>· 상태가 ready 가 아닌 영상은 분석이 끝나지 않은 것입니다. 질문 대상에서 제외하세요.</t>
         </is>
@@ -6676,9 +10334,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A50:H50"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A53:H53"/>
+    <mergeCell ref="A54:H54"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -6697,6 +10355,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
